--- a/research/traditional_assets/database/data/hong_kong/hong_kong_homebuilding.xlsx
+++ b/research/traditional_assets/database/data/hong_kong/hong_kong_homebuilding.xlsx
@@ -1380,43 +1380,43 @@
         <v>388.050314465409</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>931.6726105466551</v>
       </c>
       <c r="G2">
         <v>0.082574568288854</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.020668759811617</v>
       </c>
       <c r="I2">
         <v>0.0399513899437946</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>126.4</v>
       </c>
       <c r="L2">
-        <v>131.831874402898</v>
+        <v>130.333868229795</v>
       </c>
       <c r="M2">
         <v>-75.04000000000001</v>
       </c>
       <c r="N2">
-        <v>-74.86812559710209</v>
+        <v>-75.04953177020469</v>
       </c>
       <c r="O2">
         <v>5.26</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>1.3166</v>
       </c>
       <c r="Q2">
         <v>0.095213862842814</v>
       </c>
       <c r="R2">
-        <v>0.0953273020147347</v>
+        <v>0.09520758696641041</v>
       </c>
       <c r="S2">
         <v>0.051132574913216</v>
@@ -1438,13 +1438,13 @@
         <v>0.0970482582107704</v>
       </c>
       <c r="X2">
-        <v>0.0953273020147347</v>
+        <v>0.09574503228930339</v>
       </c>
       <c r="Y2">
         <v>0.998923940860761</v>
       </c>
       <c r="Z2">
-        <v>0.965379301385941</v>
+        <v>0.973521641958237</v>
       </c>
       <c r="AA2">
         <v>5.26</v>
@@ -1525,7 +1525,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1662,22 +1662,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09532730201473467</v>
+        <v>0.09520758696641037</v>
       </c>
       <c r="C2">
-        <v>131.8318744028979</v>
+        <v>130.3338682297953</v>
       </c>
       <c r="D2">
-        <v>-74.86812559710211</v>
+        <v>-75.04953177020465</v>
       </c>
       <c r="E2">
-        <v>-5.26</v>
+        <v>-3.9434</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.3166</v>
       </c>
       <c r="G2">
         <v>206.7</v>
@@ -1698,28 +1698,28 @@
         <v>61.7</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.06622498</v>
       </c>
       <c r="N2">
-        <v>61.7</v>
+        <v>61.63377502</v>
       </c>
       <c r="O2">
-        <v>10.1805</v>
+        <v>10.1695728783</v>
       </c>
       <c r="P2">
-        <v>51.5195</v>
+        <v>51.4642021417</v>
       </c>
       <c r="Q2">
-        <v>53.5195</v>
+        <v>53.4642021417</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09532730201473467</v>
+        <v>0.09574503228930339</v>
       </c>
       <c r="T2">
-        <v>0.9653793013859414</v>
+        <v>0.973521641958237</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>931.6726105466547</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1744,22 +1744,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09520758696641037</v>
+        <v>0.09508787191808604</v>
       </c>
       <c r="C3">
-        <v>130.3338682297953</v>
+        <v>128.8349808237268</v>
       </c>
       <c r="D3">
-        <v>-75.04953177020465</v>
+        <v>-75.23181917627323</v>
       </c>
       <c r="E3">
-        <v>-3.9434</v>
+        <v>-2.6268</v>
       </c>
       <c r="F3">
-        <v>1.3166</v>
+        <v>2.6332</v>
       </c>
       <c r="G3">
         <v>206.7</v>
@@ -1780,28 +1780,28 @@
         <v>61.7</v>
       </c>
       <c r="M3">
-        <v>0.06622498</v>
+        <v>0.13244996</v>
       </c>
       <c r="N3">
-        <v>61.63377502</v>
+        <v>61.56755004</v>
       </c>
       <c r="O3">
-        <v>10.1695728783</v>
+        <v>10.1586457566</v>
       </c>
       <c r="P3">
-        <v>51.4642021417</v>
+        <v>51.4089042834</v>
       </c>
       <c r="Q3">
-        <v>53.4642021417</v>
+        <v>53.4089042834</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09574503228930339</v>
+        <v>0.09617128767151636</v>
       </c>
       <c r="T3">
-        <v>0.973521641958237</v>
+        <v>0.9818301527462936</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>931.6726105466547</v>
+        <v>465.8363052733274</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1826,22 +1826,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09508787191808604</v>
+        <v>0.09496815686976175</v>
       </c>
       <c r="C4">
-        <v>128.8349808237268</v>
+        <v>127.3352057477916</v>
       </c>
       <c r="D4">
-        <v>-75.23181917627323</v>
+        <v>-75.41499425220842</v>
       </c>
       <c r="E4">
-        <v>-2.6268</v>
+        <v>-1.3102</v>
       </c>
       <c r="F4">
-        <v>2.6332</v>
+        <v>3.9498</v>
       </c>
       <c r="G4">
         <v>206.7</v>
@@ -1862,28 +1862,28 @@
         <v>61.7</v>
       </c>
       <c r="M4">
-        <v>0.13244996</v>
+        <v>0.19867494</v>
       </c>
       <c r="N4">
-        <v>61.56755004</v>
+        <v>61.50132506000001</v>
       </c>
       <c r="O4">
-        <v>10.1586457566</v>
+        <v>10.1477186349</v>
       </c>
       <c r="P4">
-        <v>51.4089042834</v>
+        <v>51.3536064251</v>
       </c>
       <c r="Q4">
-        <v>53.4089042834</v>
+        <v>53.3536064251</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09617128767151636</v>
+        <v>0.09660633182449664</v>
       </c>
       <c r="T4">
-        <v>0.9818301527462936</v>
+        <v>0.9903099730351351</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>465.8363052733274</v>
+        <v>310.557536848885</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1908,22 +1908,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09496815686976175</v>
+        <v>0.09484844182143744</v>
       </c>
       <c r="C5">
-        <v>127.3352057477916</v>
+        <v>125.8345365022455</v>
       </c>
       <c r="D5">
-        <v>-75.41499425220842</v>
+        <v>-75.59906349775446</v>
       </c>
       <c r="E5">
-        <v>-1.3102</v>
+        <v>0.006400000000000183</v>
       </c>
       <c r="F5">
-        <v>3.9498</v>
+        <v>5.2664</v>
       </c>
       <c r="G5">
         <v>206.7</v>
@@ -1944,28 +1944,28 @@
         <v>61.7</v>
       </c>
       <c r="M5">
-        <v>0.19867494</v>
+        <v>0.26489992</v>
       </c>
       <c r="N5">
-        <v>61.50132506000001</v>
+        <v>61.43510008000001</v>
       </c>
       <c r="O5">
-        <v>10.1477186349</v>
+        <v>10.1367915132</v>
       </c>
       <c r="P5">
-        <v>51.3536064251</v>
+        <v>51.2983085668</v>
       </c>
       <c r="Q5">
-        <v>53.3536064251</v>
+        <v>53.2983085668</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09660633182449664</v>
+        <v>0.09705043939733066</v>
       </c>
       <c r="T5">
-        <v>0.9903099730351351</v>
+        <v>0.9989664562466607</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>310.557536848885</v>
+        <v>232.9181526366637</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1990,22 +1990,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09484844182143744</v>
+        <v>0.09472872677311311</v>
       </c>
       <c r="C6">
-        <v>125.8345365022455</v>
+        <v>124.3329665237322</v>
       </c>
       <c r="D6">
-        <v>-75.59906349775446</v>
+        <v>-75.78403347626778</v>
       </c>
       <c r="E6">
-        <v>0.006400000000000183</v>
+        <v>1.323</v>
       </c>
       <c r="F6">
-        <v>5.2664</v>
+        <v>6.583</v>
       </c>
       <c r="G6">
         <v>206.7</v>
@@ -2026,28 +2026,28 @@
         <v>61.7</v>
       </c>
       <c r="M6">
-        <v>0.26489992</v>
+        <v>0.3311249</v>
       </c>
       <c r="N6">
-        <v>61.43510008000001</v>
+        <v>61.3688751</v>
       </c>
       <c r="O6">
-        <v>10.1367915132</v>
+        <v>10.1258643915</v>
       </c>
       <c r="P6">
-        <v>51.2983085668</v>
+        <v>51.2430107085</v>
       </c>
       <c r="Q6">
-        <v>53.2983085668</v>
+        <v>53.2430107085</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09705043939733066</v>
+        <v>0.09750389660327696</v>
       </c>
       <c r="T6">
-        <v>0.9989664562466607</v>
+        <v>1.007805181210008</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2064,7 +2064,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>232.9181526366637</v>
+        <v>186.334522109331</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2072,22 +2072,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09472872677311311</v>
+        <v>0.09460901172478882</v>
       </c>
       <c r="C7">
-        <v>124.3329665237322</v>
+        <v>122.8304891845028</v>
       </c>
       <c r="D7">
-        <v>-75.78403347626778</v>
+        <v>-75.96991081549722</v>
       </c>
       <c r="E7">
-        <v>1.323</v>
+        <v>2.639600000000001</v>
       </c>
       <c r="F7">
-        <v>6.583</v>
+        <v>7.8996</v>
       </c>
       <c r="G7">
         <v>206.7</v>
@@ -2108,28 +2108,28 @@
         <v>61.7</v>
       </c>
       <c r="M7">
-        <v>0.3311249</v>
+        <v>0.39734988</v>
       </c>
       <c r="N7">
-        <v>61.3688751</v>
+        <v>61.30265012</v>
       </c>
       <c r="O7">
-        <v>10.1258643915</v>
+        <v>10.1149372698</v>
       </c>
       <c r="P7">
-        <v>51.2430107085</v>
+        <v>51.1877128502</v>
       </c>
       <c r="Q7">
-        <v>53.2430107085</v>
+        <v>53.1877128502</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09750389660327696</v>
+        <v>0.09796700183488172</v>
       </c>
       <c r="T7">
-        <v>1.007805181210008</v>
+        <v>1.016831964151299</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2146,7 +2146,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>186.334522109331</v>
+        <v>155.2787684244425</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2154,22 +2154,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09460901172478881</v>
+        <v>0.0944892966764645</v>
       </c>
       <c r="C8">
-        <v>122.8304891845028</v>
+        <v>121.3270977916243</v>
       </c>
       <c r="D8">
-        <v>-75.96991081549723</v>
+        <v>-76.15670220837571</v>
       </c>
       <c r="E8">
-        <v>2.6396</v>
+        <v>3.956199999999999</v>
       </c>
       <c r="F8">
-        <v>7.8996</v>
+        <v>9.216199999999999</v>
       </c>
       <c r="G8">
         <v>206.7</v>
@@ -2190,28 +2190,28 @@
         <v>61.7</v>
       </c>
       <c r="M8">
-        <v>0.3973498799999999</v>
+        <v>0.4635748599999999</v>
       </c>
       <c r="N8">
-        <v>61.30265012</v>
+        <v>61.23642514</v>
       </c>
       <c r="O8">
-        <v>10.1149372698</v>
+        <v>10.1040101481</v>
       </c>
       <c r="P8">
-        <v>51.1877128502</v>
+        <v>51.1324149919</v>
       </c>
       <c r="Q8">
-        <v>53.1877128502</v>
+        <v>53.1324149919</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09796700183488172</v>
+        <v>0.09844006631877902</v>
       </c>
       <c r="T8">
-        <v>1.016831964151299</v>
+        <v>1.026052871456918</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>155.2787684244425</v>
+        <v>133.0960872209507</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2236,22 +2236,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09448929667646448</v>
+        <v>0.09436958162814017</v>
       </c>
       <c r="C9">
-        <v>121.3270977916243</v>
+        <v>119.8227855861765</v>
       </c>
       <c r="D9">
-        <v>-76.15670220837572</v>
+        <v>-76.34441441382354</v>
       </c>
       <c r="E9">
-        <v>3.956200000000001</v>
+        <v>5.2728</v>
       </c>
       <c r="F9">
-        <v>9.216200000000001</v>
+        <v>10.5328</v>
       </c>
       <c r="G9">
         <v>206.7</v>
@@ -2272,28 +2272,28 @@
         <v>61.7</v>
       </c>
       <c r="M9">
-        <v>0.46357486</v>
+        <v>0.52979984</v>
       </c>
       <c r="N9">
-        <v>61.23642514</v>
+        <v>61.17020016</v>
       </c>
       <c r="O9">
-        <v>10.1040101481</v>
+        <v>10.0930830264</v>
       </c>
       <c r="P9">
-        <v>51.1324149919</v>
+        <v>51.0771171336</v>
       </c>
       <c r="Q9">
-        <v>53.1324149919</v>
+        <v>53.0771171336</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09844006631877902</v>
+        <v>0.09892341481319585</v>
       </c>
       <c r="T9">
-        <v>1.026052871456918</v>
+        <v>1.035474233269182</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>133.0960872209507</v>
+        <v>116.4590763183318</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2318,22 +2318,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09436958162814017</v>
+        <v>0.09424986657981586</v>
       </c>
       <c r="C10">
-        <v>119.8227855861765</v>
+        <v>118.3175457424364</v>
       </c>
       <c r="D10">
-        <v>-76.34441441382354</v>
+        <v>-76.53305425756358</v>
       </c>
       <c r="E10">
-        <v>5.2728</v>
+        <v>6.589399999999999</v>
       </c>
       <c r="F10">
-        <v>10.5328</v>
+        <v>11.8494</v>
       </c>
       <c r="G10">
         <v>206.7</v>
@@ -2354,28 +2354,28 @@
         <v>61.7</v>
       </c>
       <c r="M10">
-        <v>0.52979984</v>
+        <v>0.5960248199999999</v>
       </c>
       <c r="N10">
-        <v>61.17020016</v>
+        <v>61.10397518000001</v>
       </c>
       <c r="O10">
-        <v>10.0930830264</v>
+        <v>10.0821559047</v>
       </c>
       <c r="P10">
-        <v>51.0771171336</v>
+        <v>51.0218192753</v>
       </c>
       <c r="Q10">
-        <v>53.0771171336</v>
+        <v>53.0218192753</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09892341481319585</v>
+        <v>0.09941738635144601</v>
       </c>
       <c r="T10">
-        <v>1.035474233269182</v>
+        <v>1.045102657978418</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>116.4590763183318</v>
+        <v>103.5191789496283</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2400,22 +2400,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09424986657981586</v>
+        <v>0.09413015153149155</v>
       </c>
       <c r="C11">
-        <v>118.3175457424364</v>
+        <v>116.8113713670513</v>
       </c>
       <c r="D11">
-        <v>-76.53305425756358</v>
+        <v>-76.7226286329487</v>
       </c>
       <c r="E11">
-        <v>6.589399999999999</v>
+        <v>7.905999999999999</v>
       </c>
       <c r="F11">
-        <v>11.8494</v>
+        <v>13.166</v>
       </c>
       <c r="G11">
         <v>206.7</v>
@@ -2436,28 +2436,28 @@
         <v>61.7</v>
       </c>
       <c r="M11">
-        <v>0.5960248199999999</v>
+        <v>0.6622497999999999</v>
       </c>
       <c r="N11">
-        <v>61.10397518000001</v>
+        <v>61.0377502</v>
       </c>
       <c r="O11">
-        <v>10.0821559047</v>
+        <v>10.071228783</v>
       </c>
       <c r="P11">
-        <v>51.0218192753</v>
+        <v>50.966521417</v>
       </c>
       <c r="Q11">
-        <v>53.0218192753</v>
+        <v>52.966521417</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09941738635144601</v>
+        <v>0.09992233503499062</v>
       </c>
       <c r="T11">
-        <v>1.045102657978418</v>
+        <v>1.054945047681193</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>103.5191789496283</v>
+        <v>93.1672610546655</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2482,22 +2482,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09413015153149155</v>
+        <v>0.09401043648316723</v>
       </c>
       <c r="C12">
-        <v>116.8113713670513</v>
+        <v>115.3042554981985</v>
       </c>
       <c r="D12">
-        <v>-76.7226286329487</v>
+        <v>-76.9131445018015</v>
       </c>
       <c r="E12">
-        <v>7.906000000000001</v>
+        <v>9.2226</v>
       </c>
       <c r="F12">
-        <v>13.166</v>
+        <v>14.4826</v>
       </c>
       <c r="G12">
         <v>206.7</v>
@@ -2518,28 +2518,28 @@
         <v>61.7</v>
       </c>
       <c r="M12">
-        <v>0.6622498</v>
+        <v>0.72847478</v>
       </c>
       <c r="N12">
-        <v>61.0377502</v>
+        <v>60.97152522</v>
       </c>
       <c r="O12">
-        <v>10.071228783</v>
+        <v>10.0603016613</v>
       </c>
       <c r="P12">
-        <v>50.966521417</v>
+        <v>50.9112235587</v>
       </c>
       <c r="Q12">
-        <v>52.966521417</v>
+        <v>52.9112235587</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09992233503499062</v>
+        <v>0.1004386308799632</v>
       </c>
       <c r="T12">
-        <v>1.054945047681193</v>
+        <v>1.065008614680659</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>93.16726105466549</v>
+        <v>84.69751004969589</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2564,22 +2564,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09401043648316723</v>
+        <v>0.09389072143484292</v>
       </c>
       <c r="C13">
-        <v>115.3042554981985</v>
+        <v>113.7961911047337</v>
       </c>
       <c r="D13">
-        <v>-76.9131445018015</v>
+        <v>-77.10460889526632</v>
       </c>
       <c r="E13">
-        <v>9.2226</v>
+        <v>10.5392</v>
       </c>
       <c r="F13">
-        <v>14.4826</v>
+        <v>15.7992</v>
       </c>
       <c r="G13">
         <v>206.7</v>
@@ -2600,28 +2600,28 @@
         <v>61.7</v>
       </c>
       <c r="M13">
-        <v>0.72847478</v>
+        <v>0.7946997599999999</v>
       </c>
       <c r="N13">
-        <v>60.97152522</v>
+        <v>60.90530024</v>
       </c>
       <c r="O13">
-        <v>10.0603016613</v>
+        <v>10.0493745396</v>
       </c>
       <c r="P13">
-        <v>50.9112235587</v>
+        <v>50.8559257004</v>
       </c>
       <c r="Q13">
-        <v>52.9112235587</v>
+        <v>52.8559257004</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1004386308799632</v>
+        <v>0.1009666607214124</v>
       </c>
       <c r="T13">
-        <v>1.065008614680659</v>
+        <v>1.075300899111931</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2638,7 +2638,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>84.69751004969589</v>
+        <v>77.63938421222124</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2646,22 +2646,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09389072143484292</v>
+        <v>0.09377100638651861</v>
       </c>
       <c r="C14">
-        <v>113.7961911047337</v>
+        <v>112.2871710853255</v>
       </c>
       <c r="D14">
-        <v>-77.10460889526632</v>
+        <v>-77.29702891467448</v>
       </c>
       <c r="E14">
-        <v>10.5392</v>
+        <v>11.8558</v>
       </c>
       <c r="F14">
-        <v>15.7992</v>
+        <v>17.1158</v>
       </c>
       <c r="G14">
         <v>206.7</v>
@@ -2682,28 +2682,28 @@
         <v>61.7</v>
       </c>
       <c r="M14">
-        <v>0.7946997599999999</v>
+        <v>0.86092474</v>
       </c>
       <c r="N14">
-        <v>60.90530024</v>
+        <v>60.83907526</v>
       </c>
       <c r="O14">
-        <v>10.0493745396</v>
+        <v>10.0384474179</v>
       </c>
       <c r="P14">
-        <v>50.8559257004</v>
+        <v>50.8006278421</v>
       </c>
       <c r="Q14">
-        <v>52.8559257004</v>
+        <v>52.8006278421</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1009666607214124</v>
+        <v>0.1015068291799065</v>
       </c>
       <c r="T14">
-        <v>1.075300899111931</v>
+        <v>1.085829787783003</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2720,7 +2720,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>77.63938421222124</v>
+        <v>71.66712388820422</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2728,22 +2728,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09377100638651861</v>
+        <v>0.09365129133819432</v>
       </c>
       <c r="C15">
-        <v>112.2871710853255</v>
+        <v>110.7771882675778</v>
       </c>
       <c r="D15">
-        <v>-77.29702891467448</v>
+        <v>-77.49041173242216</v>
       </c>
       <c r="E15">
-        <v>11.8558</v>
+        <v>13.1724</v>
       </c>
       <c r="F15">
-        <v>17.1158</v>
+        <v>18.4324</v>
       </c>
       <c r="G15">
         <v>206.7</v>
@@ -2764,28 +2764,28 @@
         <v>61.7</v>
       </c>
       <c r="M15">
-        <v>0.86092474</v>
+        <v>0.9271497200000001</v>
       </c>
       <c r="N15">
-        <v>60.83907526</v>
+        <v>60.77285028</v>
       </c>
       <c r="O15">
-        <v>10.0384474179</v>
+        <v>10.0275202962</v>
       </c>
       <c r="P15">
-        <v>50.8006278421</v>
+        <v>50.7453299838</v>
       </c>
       <c r="Q15">
-        <v>52.8006278421</v>
+        <v>52.7453299838</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1015068291799065</v>
+        <v>0.1020595596955748</v>
       </c>
       <c r="T15">
-        <v>1.085829787783003</v>
+        <v>1.096603534330147</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>71.66712388820422</v>
+        <v>66.54804361047533</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2810,22 +2810,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09365129133819432</v>
+        <v>0.09353157628986999</v>
       </c>
       <c r="C16">
-        <v>110.7771882675778</v>
+        <v>109.2662354071384</v>
       </c>
       <c r="D16">
-        <v>-77.49041173242216</v>
+        <v>-77.68476459286158</v>
       </c>
       <c r="E16">
-        <v>13.1724</v>
+        <v>14.489</v>
       </c>
       <c r="F16">
-        <v>18.4324</v>
+        <v>19.749</v>
       </c>
       <c r="G16">
         <v>206.7</v>
@@ -2846,28 +2846,28 @@
         <v>61.7</v>
       </c>
       <c r="M16">
-        <v>0.9271497200000001</v>
+        <v>0.9933747000000001</v>
       </c>
       <c r="N16">
-        <v>60.77285028</v>
+        <v>60.70662530000001</v>
       </c>
       <c r="O16">
-        <v>10.0275202962</v>
+        <v>10.0165931745</v>
       </c>
       <c r="P16">
-        <v>50.7453299838</v>
+        <v>50.6900321255</v>
       </c>
       <c r="Q16">
-        <v>52.7453299838</v>
+        <v>52.6900321255</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1020595596955748</v>
+        <v>0.1026252956351412</v>
       </c>
       <c r="T16">
-        <v>1.096603534330147</v>
+        <v>1.107630780796046</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2884,7 +2884,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>66.54804361047533</v>
+        <v>62.11150736977699</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2892,22 +2892,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09353157628986999</v>
+        <v>0.09341186124154567</v>
       </c>
       <c r="C17">
-        <v>109.2662354071384</v>
+        <v>107.7543051867944</v>
       </c>
       <c r="D17">
-        <v>-77.68476459286158</v>
+        <v>-77.88009481320556</v>
       </c>
       <c r="E17">
-        <v>14.489</v>
+        <v>15.8056</v>
       </c>
       <c r="F17">
-        <v>19.749</v>
+        <v>21.0656</v>
       </c>
       <c r="G17">
         <v>206.7</v>
@@ -2928,28 +2928,28 @@
         <v>61.7</v>
       </c>
       <c r="M17">
-        <v>0.9933746999999999</v>
+        <v>1.05959968</v>
       </c>
       <c r="N17">
-        <v>60.70662530000001</v>
+        <v>60.64040032</v>
       </c>
       <c r="O17">
-        <v>10.0165931745</v>
+        <v>10.0056660528</v>
       </c>
       <c r="P17">
-        <v>50.6900321255</v>
+        <v>50.6347342672</v>
       </c>
       <c r="Q17">
-        <v>52.6900321255</v>
+        <v>52.6347342672</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1026252956351412</v>
+        <v>0.1032045014780306</v>
       </c>
       <c r="T17">
-        <v>1.107630780796046</v>
+        <v>1.118920580749229</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>62.11150736977699</v>
+        <v>58.22953815916593</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2974,22 +2974,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09341186124154567</v>
+        <v>0.09329214619322138</v>
       </c>
       <c r="C18">
-        <v>107.7543051867944</v>
+        <v>106.2413902155541</v>
       </c>
       <c r="D18">
-        <v>-77.88009481320556</v>
+        <v>-78.07640978444589</v>
       </c>
       <c r="E18">
-        <v>15.8056</v>
+        <v>17.1222</v>
       </c>
       <c r="F18">
-        <v>21.0656</v>
+        <v>22.3822</v>
       </c>
       <c r="G18">
         <v>206.7</v>
@@ -3010,28 +3010,28 @@
         <v>61.7</v>
       </c>
       <c r="M18">
-        <v>1.05959968</v>
+        <v>1.12582466</v>
       </c>
       <c r="N18">
-        <v>60.64040032</v>
+        <v>60.57417534</v>
       </c>
       <c r="O18">
-        <v>10.0056660528</v>
+        <v>9.994738931100001</v>
       </c>
       <c r="P18">
-        <v>50.6347342672</v>
+        <v>50.5794364089</v>
       </c>
       <c r="Q18">
-        <v>52.6347342672</v>
+        <v>52.5794364089</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1032045014780306</v>
+        <v>0.1037976640882185</v>
       </c>
       <c r="T18">
-        <v>1.118920580749229</v>
+        <v>1.130482424074778</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -3048,7 +3048,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>58.22953815916593</v>
+        <v>54.80427120862676</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3056,22 +3056,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09329214619322138</v>
+        <v>0.09317243114489707</v>
       </c>
       <c r="C19">
-        <v>106.2413902155541</v>
+        <v>104.7274830277143</v>
       </c>
       <c r="D19">
-        <v>-78.07640978444589</v>
+        <v>-78.27371697228567</v>
       </c>
       <c r="E19">
-        <v>17.1222</v>
+        <v>18.4388</v>
       </c>
       <c r="F19">
-        <v>22.3822</v>
+        <v>23.6988</v>
       </c>
       <c r="G19">
         <v>206.7</v>
@@ -3092,28 +3092,28 @@
         <v>61.7</v>
       </c>
       <c r="M19">
-        <v>1.12582466</v>
+        <v>1.19204964</v>
       </c>
       <c r="N19">
-        <v>60.57417534</v>
+        <v>60.50795036</v>
       </c>
       <c r="O19">
-        <v>9.994738931100001</v>
+        <v>9.983811809400001</v>
       </c>
       <c r="P19">
-        <v>50.5794364089</v>
+        <v>50.5241385506</v>
       </c>
       <c r="Q19">
-        <v>52.5794364089</v>
+        <v>52.5241385506</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1037976640882185</v>
+        <v>0.1044052940791428</v>
       </c>
       <c r="T19">
-        <v>1.130482424074778</v>
+        <v>1.142326263578999</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3130,7 +3130,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>54.80427120862676</v>
+        <v>51.75958947481416</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3138,22 +3138,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09317243114489707</v>
+        <v>0.09305271609657276</v>
       </c>
       <c r="C20">
-        <v>104.7274830277143</v>
+        <v>103.2125760819144</v>
       </c>
       <c r="D20">
-        <v>-78.27371697228567</v>
+        <v>-78.47202391808555</v>
       </c>
       <c r="E20">
-        <v>18.4388</v>
+        <v>19.7554</v>
       </c>
       <c r="F20">
-        <v>23.6988</v>
+        <v>25.0154</v>
       </c>
       <c r="G20">
         <v>206.7</v>
@@ -3174,28 +3174,28 @@
         <v>61.7</v>
       </c>
       <c r="M20">
-        <v>1.19204964</v>
+        <v>1.25827462</v>
       </c>
       <c r="N20">
-        <v>60.50795036</v>
+        <v>60.44172538</v>
       </c>
       <c r="O20">
-        <v>9.983811809400001</v>
+        <v>9.972884687700001</v>
       </c>
       <c r="P20">
-        <v>50.5241385506</v>
+        <v>50.4688406923</v>
       </c>
       <c r="Q20">
-        <v>52.5241385506</v>
+        <v>52.4688406923</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1044052940791428</v>
+        <v>0.1050279272797194</v>
       </c>
       <c r="T20">
-        <v>1.142326263578999</v>
+        <v>1.154462543564805</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3212,7 +3212,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>51.75958947481416</v>
+        <v>49.03540055508709</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3220,22 +3220,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09305271609657276</v>
+        <v>0.09293300104824843</v>
       </c>
       <c r="C21">
-        <v>103.2125760819144</v>
+        <v>101.6966617601753</v>
       </c>
       <c r="D21">
-        <v>-78.47202391808555</v>
+        <v>-78.67133823982468</v>
       </c>
       <c r="E21">
-        <v>19.7554</v>
+        <v>21.072</v>
       </c>
       <c r="F21">
-        <v>25.0154</v>
+        <v>26.332</v>
       </c>
       <c r="G21">
         <v>206.7</v>
@@ -3256,28 +3256,28 @@
         <v>61.7</v>
       </c>
       <c r="M21">
-        <v>1.25827462</v>
+        <v>1.3244996</v>
       </c>
       <c r="N21">
-        <v>60.44172538</v>
+        <v>60.3755004</v>
       </c>
       <c r="O21">
-        <v>9.972884687700001</v>
+        <v>9.961957566000001</v>
       </c>
       <c r="P21">
-        <v>50.4688406923</v>
+        <v>50.413542834</v>
       </c>
       <c r="Q21">
-        <v>52.4688406923</v>
+        <v>52.413542834</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1050279272797194</v>
+        <v>0.1056661263103105</v>
       </c>
       <c r="T21">
-        <v>1.154462543564805</v>
+        <v>1.166902230550257</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3294,7 +3294,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>49.03540055508709</v>
+        <v>46.58363052733274</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3302,22 +3302,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09293300104824843</v>
+        <v>0.09281328599992411</v>
       </c>
       <c r="C22">
-        <v>101.6966617601753</v>
+        <v>100.1797323669239</v>
       </c>
       <c r="D22">
-        <v>-78.67133823982468</v>
+        <v>-78.8716676330761</v>
       </c>
       <c r="E22">
-        <v>21.072</v>
+        <v>22.3886</v>
       </c>
       <c r="F22">
-        <v>26.332</v>
+        <v>27.6486</v>
       </c>
       <c r="G22">
         <v>206.7</v>
@@ -3338,28 +3338,28 @@
         <v>61.7</v>
       </c>
       <c r="M22">
-        <v>1.3244996</v>
+        <v>1.39072458</v>
       </c>
       <c r="N22">
-        <v>60.3755004</v>
+        <v>60.30927542000001</v>
       </c>
       <c r="O22">
-        <v>9.961957566000001</v>
+        <v>9.951030444300001</v>
       </c>
       <c r="P22">
-        <v>50.413542834</v>
+        <v>50.3582449757</v>
       </c>
       <c r="Q22">
-        <v>52.413542834</v>
+        <v>52.3582449757</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1056661263103105</v>
+        <v>0.1063204822783849</v>
       </c>
       <c r="T22">
-        <v>1.166902230550257</v>
+        <v>1.17965684632015</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3376,7 +3376,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>46.58363052733274</v>
+        <v>44.36536240698356</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3384,22 +3384,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09281328599992411</v>
+        <v>0.0926935709515998</v>
       </c>
       <c r="C23">
-        <v>100.1797323669239</v>
+        <v>98.66178012800275</v>
       </c>
       <c r="D23">
-        <v>-78.8716676330761</v>
+        <v>-79.07301987199725</v>
       </c>
       <c r="E23">
-        <v>22.3886</v>
+        <v>23.7052</v>
       </c>
       <c r="F23">
-        <v>27.6486</v>
+        <v>28.9652</v>
       </c>
       <c r="G23">
         <v>206.7</v>
@@ -3420,28 +3420,28 @@
         <v>61.7</v>
       </c>
       <c r="M23">
-        <v>1.39072458</v>
+        <v>1.45694956</v>
       </c>
       <c r="N23">
-        <v>60.30927542000001</v>
+        <v>60.24305044</v>
       </c>
       <c r="O23">
-        <v>9.951030444300001</v>
+        <v>9.940103322600001</v>
       </c>
       <c r="P23">
-        <v>50.3582449757</v>
+        <v>50.3029471174</v>
       </c>
       <c r="Q23">
-        <v>52.3582449757</v>
+        <v>52.3029471174</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1063204822783849</v>
+        <v>0.1069916166046151</v>
       </c>
       <c r="T23">
-        <v>1.17965684632015</v>
+        <v>1.192738503520041</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>44.36536240698356</v>
+        <v>42.34875502484795</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3466,22 +3466,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0926935709515998</v>
+        <v>0.09257385590327548</v>
       </c>
       <c r="C24">
-        <v>98.66178012800275</v>
+        <v>97.14279718966424</v>
       </c>
       <c r="D24">
-        <v>-79.07301987199725</v>
+        <v>-79.27540281033575</v>
       </c>
       <c r="E24">
-        <v>23.7052</v>
+        <v>25.0218</v>
       </c>
       <c r="F24">
-        <v>28.9652</v>
+        <v>30.2818</v>
       </c>
       <c r="G24">
         <v>206.7</v>
@@ -3502,28 +3502,28 @@
         <v>61.7</v>
       </c>
       <c r="M24">
-        <v>1.45694956</v>
+        <v>1.52317454</v>
       </c>
       <c r="N24">
-        <v>60.24305044</v>
+        <v>60.17682546</v>
       </c>
       <c r="O24">
-        <v>9.940103322600001</v>
+        <v>9.929176200900001</v>
       </c>
       <c r="P24">
-        <v>50.3029471174</v>
+        <v>50.2476492591</v>
       </c>
       <c r="Q24">
-        <v>52.3029471174</v>
+        <v>52.2476492591</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1069916166046151</v>
+        <v>0.1076801829912669</v>
       </c>
       <c r="T24">
-        <v>1.192738503520041</v>
+        <v>1.206159944023824</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3540,7 +3540,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>42.34875502484795</v>
+        <v>40.5075048063763</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3548,22 +3548,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09257385590327548</v>
+        <v>0.09245414085495117</v>
       </c>
       <c r="C25">
-        <v>97.14279718966424</v>
+        <v>95.62277561754968</v>
       </c>
       <c r="D25">
-        <v>-79.27540281033575</v>
+        <v>-79.47882438245031</v>
       </c>
       <c r="E25">
-        <v>25.0218</v>
+        <v>26.3384</v>
       </c>
       <c r="F25">
-        <v>30.2818</v>
+        <v>31.5984</v>
       </c>
       <c r="G25">
         <v>206.7</v>
@@ -3584,28 +3584,28 @@
         <v>61.7</v>
       </c>
       <c r="M25">
-        <v>1.52317454</v>
+        <v>1.58939952</v>
       </c>
       <c r="N25">
-        <v>60.17682546</v>
+        <v>60.11060048</v>
       </c>
       <c r="O25">
-        <v>9.929176200900001</v>
+        <v>9.918249079200001</v>
       </c>
       <c r="P25">
-        <v>50.2476492591</v>
+        <v>50.1923514008</v>
       </c>
       <c r="Q25">
-        <v>52.2476492591</v>
+        <v>52.1923514008</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1076801829912669</v>
+        <v>0.1083868695459884</v>
       </c>
       <c r="T25">
-        <v>1.206159944023824</v>
+        <v>1.21993458033034</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>40.5075048063763</v>
+        <v>38.81969210611062</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3630,22 +3630,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09245414085495117</v>
+        <v>0.09233442580662687</v>
       </c>
       <c r="C26">
-        <v>95.62277561754968</v>
+        <v>94.10170739565217</v>
       </c>
       <c r="D26">
-        <v>-79.47882438245031</v>
+        <v>-79.68329260434783</v>
       </c>
       <c r="E26">
-        <v>26.3384</v>
+        <v>27.655</v>
       </c>
       <c r="F26">
-        <v>31.5984</v>
+        <v>32.915</v>
       </c>
       <c r="G26">
         <v>206.7</v>
@@ -3666,28 +3666,28 @@
         <v>61.7</v>
       </c>
       <c r="M26">
-        <v>1.58939952</v>
+        <v>1.6556245</v>
       </c>
       <c r="N26">
-        <v>60.11060048</v>
+        <v>60.0443755</v>
       </c>
       <c r="O26">
-        <v>9.918249079200001</v>
+        <v>9.907321957500001</v>
       </c>
       <c r="P26">
-        <v>50.1923514008</v>
+        <v>50.1370535425</v>
       </c>
       <c r="Q26">
-        <v>52.1923514008</v>
+        <v>52.1370535425</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1083868695459884</v>
+        <v>0.1091124010755025</v>
       </c>
       <c r="T26">
-        <v>1.21993458033034</v>
+        <v>1.234076540271695</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>38.81969210611062</v>
+        <v>37.26690442186619</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3712,22 +3712,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09233442580662687</v>
+        <v>0.09221471075830255</v>
       </c>
       <c r="C27">
-        <v>94.10170739565217</v>
+        <v>92.57958442526363</v>
       </c>
       <c r="D27">
-        <v>-79.68329260434783</v>
+        <v>-79.88881557473636</v>
       </c>
       <c r="E27">
-        <v>27.655</v>
+        <v>28.9716</v>
       </c>
       <c r="F27">
-        <v>32.915</v>
+        <v>34.2316</v>
       </c>
       <c r="G27">
         <v>206.7</v>
@@ -3748,28 +3748,28 @@
         <v>61.7</v>
       </c>
       <c r="M27">
-        <v>1.6556245</v>
+        <v>1.72184948</v>
       </c>
       <c r="N27">
-        <v>60.0443755</v>
+        <v>59.97815052</v>
       </c>
       <c r="O27">
-        <v>9.907321957500001</v>
+        <v>9.896394835800001</v>
       </c>
       <c r="P27">
-        <v>50.1370535425</v>
+        <v>50.0817556842</v>
       </c>
       <c r="Q27">
-        <v>52.1370535425</v>
+        <v>52.0817556842</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1091124010755025</v>
+        <v>0.1098575415652737</v>
       </c>
       <c r="T27">
-        <v>1.234076540271695</v>
+        <v>1.248600715346601</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3786,7 +3786,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>37.26690442186619</v>
+        <v>35.83356194410211</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3794,22 +3794,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09221471075830255</v>
+        <v>0.09209499570997823</v>
       </c>
       <c r="C28">
-        <v>92.57958442526363</v>
+        <v>91.05639852390581</v>
       </c>
       <c r="D28">
-        <v>-79.88881557473636</v>
+        <v>-80.09540147609418</v>
       </c>
       <c r="E28">
-        <v>28.9716</v>
+        <v>30.2882</v>
       </c>
       <c r="F28">
-        <v>34.2316</v>
+        <v>35.5482</v>
       </c>
       <c r="G28">
         <v>206.7</v>
@@ -3830,28 +3830,28 @@
         <v>61.7</v>
       </c>
       <c r="M28">
-        <v>1.72184948</v>
+        <v>1.78807446</v>
       </c>
       <c r="N28">
-        <v>59.97815052</v>
+        <v>59.91192554000001</v>
       </c>
       <c r="O28">
-        <v>9.896394835800001</v>
+        <v>9.885467714100001</v>
       </c>
       <c r="P28">
-        <v>50.0817556842</v>
+        <v>50.0264578259</v>
       </c>
       <c r="Q28">
-        <v>52.0817556842</v>
+        <v>52.0264578259</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1098575415652737</v>
+        <v>0.1106230968629839</v>
       </c>
       <c r="T28">
-        <v>1.248600715346601</v>
+        <v>1.263522813026298</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>35.83356194410211</v>
+        <v>34.50639298320944</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3876,22 +3876,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09209499570997823</v>
+        <v>0.09197528066165393</v>
       </c>
       <c r="C29">
-        <v>91.05639852390581</v>
+        <v>89.5321414242441</v>
       </c>
       <c r="D29">
-        <v>-80.09540147609418</v>
+        <v>-80.30305857575588</v>
       </c>
       <c r="E29">
-        <v>30.2882</v>
+        <v>31.6048</v>
       </c>
       <c r="F29">
-        <v>35.5482</v>
+        <v>36.8648</v>
       </c>
       <c r="G29">
         <v>206.7</v>
@@ -3912,28 +3912,28 @@
         <v>61.7</v>
       </c>
       <c r="M29">
-        <v>1.78807446</v>
+        <v>1.85429944</v>
       </c>
       <c r="N29">
-        <v>59.91192554000001</v>
+        <v>59.84570056</v>
       </c>
       <c r="O29">
-        <v>9.885467714100001</v>
+        <v>9.874540592400001</v>
       </c>
       <c r="P29">
-        <v>50.0264578259</v>
+        <v>49.9711599676</v>
       </c>
       <c r="Q29">
-        <v>52.0264578259</v>
+        <v>51.9711599676</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1106230968629839</v>
+        <v>0.1114099175856305</v>
       </c>
       <c r="T29">
-        <v>1.263522813026298</v>
+        <v>1.278859413419321</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>34.50639298320944</v>
+        <v>33.27402180523767</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3958,22 +3958,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09197528066165393</v>
+        <v>0.09185556561332962</v>
       </c>
       <c r="C30">
-        <v>89.5321414242441</v>
+        <v>88.00680477298465</v>
       </c>
       <c r="D30">
-        <v>-80.30305857575588</v>
+        <v>-80.51179522701534</v>
       </c>
       <c r="E30">
-        <v>31.6048</v>
+        <v>32.92140000000001</v>
       </c>
       <c r="F30">
-        <v>36.8648</v>
+        <v>38.1814</v>
       </c>
       <c r="G30">
         <v>206.7</v>
@@ -3994,28 +3994,28 @@
         <v>61.7</v>
       </c>
       <c r="M30">
-        <v>1.85429944</v>
+        <v>1.92052442</v>
       </c>
       <c r="N30">
-        <v>59.84570056</v>
+        <v>59.77947558</v>
       </c>
       <c r="O30">
-        <v>9.874540592400001</v>
+        <v>9.863613470700001</v>
       </c>
       <c r="P30">
-        <v>49.9711599676</v>
+        <v>49.9158621093</v>
       </c>
       <c r="Q30">
-        <v>51.9711599676</v>
+        <v>51.9158621093</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1114099175856305</v>
+        <v>0.1122189022722953</v>
       </c>
       <c r="T30">
-        <v>1.278859413419321</v>
+        <v>1.294628030724823</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -4032,7 +4032,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>33.27402180523767</v>
+        <v>32.1266417429881</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4040,22 +4040,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09185556561332962</v>
+        <v>0.09173585056500531</v>
       </c>
       <c r="C31">
-        <v>88.00680477298465</v>
+        <v>86.48038012975442</v>
       </c>
       <c r="D31">
-        <v>-80.51179522701534</v>
+        <v>-80.72161987024558</v>
       </c>
       <c r="E31">
-        <v>32.9214</v>
+        <v>34.238</v>
       </c>
       <c r="F31">
-        <v>38.1814</v>
+        <v>39.498</v>
       </c>
       <c r="G31">
         <v>206.7</v>
@@ -4076,28 +4076,28 @@
         <v>61.7</v>
       </c>
       <c r="M31">
-        <v>1.92052442</v>
+        <v>1.9867494</v>
       </c>
       <c r="N31">
-        <v>59.77947558</v>
+        <v>59.7132506</v>
       </c>
       <c r="O31">
-        <v>9.863613470700001</v>
+        <v>9.852686349000001</v>
       </c>
       <c r="P31">
-        <v>49.9158621093</v>
+        <v>49.860564251</v>
       </c>
       <c r="Q31">
-        <v>51.9158621093</v>
+        <v>51.860564251</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1122189022722953</v>
+        <v>0.1130510008071504</v>
       </c>
       <c r="T31">
-        <v>1.294628030724823</v>
+        <v>1.310847179953339</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>32.1266417429881</v>
+        <v>31.05575368488849</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4122,22 +4122,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09173585056500531</v>
+        <v>0.09161613551668099</v>
       </c>
       <c r="C32">
-        <v>86.48038012975442</v>
+        <v>84.95285896596343</v>
       </c>
       <c r="D32">
-        <v>-80.72161987024558</v>
+        <v>-80.93254103403656</v>
       </c>
       <c r="E32">
-        <v>34.238</v>
+        <v>35.5546</v>
       </c>
       <c r="F32">
-        <v>39.498</v>
+        <v>40.8146</v>
       </c>
       <c r="G32">
         <v>206.7</v>
@@ -4158,28 +4158,28 @@
         <v>61.7</v>
       </c>
       <c r="M32">
-        <v>1.9867494</v>
+        <v>2.05297438</v>
       </c>
       <c r="N32">
-        <v>59.7132506</v>
+        <v>59.64702562</v>
       </c>
       <c r="O32">
-        <v>9.852686349000001</v>
+        <v>9.841759227300001</v>
       </c>
       <c r="P32">
-        <v>49.860564251</v>
+        <v>49.8052663927</v>
       </c>
       <c r="Q32">
-        <v>51.860564251</v>
+        <v>51.8052663927</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1130510008071504</v>
+        <v>0.1139072181401174</v>
       </c>
       <c r="T32">
-        <v>1.310847179953339</v>
+        <v>1.327536449449349</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>31.05575368488849</v>
+        <v>30.05395517892435</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4204,22 +4204,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09161613551668099</v>
+        <v>0.09149642046835668</v>
       </c>
       <c r="C33">
-        <v>84.95285896596343</v>
+        <v>83.42423266364926</v>
       </c>
       <c r="D33">
-        <v>-80.93254103403656</v>
+        <v>-81.14456733635072</v>
       </c>
       <c r="E33">
-        <v>35.5546</v>
+        <v>36.8712</v>
       </c>
       <c r="F33">
-        <v>40.8146</v>
+        <v>42.1312</v>
       </c>
       <c r="G33">
         <v>206.7</v>
@@ -4240,28 +4240,28 @@
         <v>61.7</v>
       </c>
       <c r="M33">
-        <v>2.05297438</v>
+        <v>2.11919936</v>
       </c>
       <c r="N33">
-        <v>59.64702562</v>
+        <v>59.58080064</v>
       </c>
       <c r="O33">
-        <v>9.841759227300001</v>
+        <v>9.830832105600001</v>
       </c>
       <c r="P33">
-        <v>49.8052663927</v>
+        <v>49.7499685344</v>
       </c>
       <c r="Q33">
-        <v>51.8052663927</v>
+        <v>51.7499685344</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1139072181401174</v>
+        <v>0.1147886183358187</v>
       </c>
       <c r="T33">
-        <v>1.327536449449349</v>
+        <v>1.344716579812888</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>30.05395517892435</v>
+        <v>29.11476907958296</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4286,22 +4286,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09149642046835668</v>
+        <v>0.09137670542003236</v>
       </c>
       <c r="C34">
-        <v>83.42423266364926</v>
+        <v>81.8944925143032</v>
       </c>
       <c r="D34">
-        <v>-81.14456733635072</v>
+        <v>-81.35770748569679</v>
       </c>
       <c r="E34">
-        <v>36.8712</v>
+        <v>38.1878</v>
       </c>
       <c r="F34">
-        <v>42.1312</v>
+        <v>43.4478</v>
       </c>
       <c r="G34">
         <v>206.7</v>
@@ -4322,28 +4322,28 @@
         <v>61.7</v>
       </c>
       <c r="M34">
-        <v>2.11919936</v>
+        <v>2.18542434</v>
       </c>
       <c r="N34">
-        <v>59.58080064</v>
+        <v>59.51457566000001</v>
       </c>
       <c r="O34">
-        <v>9.830832105600001</v>
+        <v>9.819904983900001</v>
       </c>
       <c r="P34">
-        <v>49.7499685344</v>
+        <v>49.6946706761</v>
       </c>
       <c r="Q34">
-        <v>51.7499685344</v>
+        <v>51.6946706761</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1147886183358187</v>
+        <v>0.1156963289851229</v>
       </c>
       <c r="T34">
-        <v>1.344716579812888</v>
+        <v>1.362409549888771</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4360,7 +4360,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>29.11476907958296</v>
+        <v>28.23250334989863</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4368,22 +4368,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09137670542003236</v>
+        <v>0.09125699037170804</v>
       </c>
       <c r="C35">
-        <v>81.8944925143032</v>
+        <v>80.36362971767801</v>
       </c>
       <c r="D35">
-        <v>-81.35770748569679</v>
+        <v>-81.57197028232197</v>
       </c>
       <c r="E35">
-        <v>38.1878</v>
+        <v>39.5044</v>
       </c>
       <c r="F35">
-        <v>43.4478</v>
+        <v>44.7644</v>
       </c>
       <c r="G35">
         <v>206.7</v>
@@ -4404,28 +4404,28 @@
         <v>61.7</v>
       </c>
       <c r="M35">
-        <v>2.18542434</v>
+        <v>2.25164932</v>
       </c>
       <c r="N35">
-        <v>59.51457566000001</v>
+        <v>59.44835068</v>
       </c>
       <c r="O35">
-        <v>9.819904983900001</v>
+        <v>9.808977862200001</v>
       </c>
       <c r="P35">
-        <v>49.6946706761</v>
+        <v>49.6393728178</v>
       </c>
       <c r="Q35">
-        <v>51.6946706761</v>
+        <v>51.6393728178</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1156963289851229</v>
+        <v>0.1166315460177395</v>
       </c>
       <c r="T35">
-        <v>1.362409549888771</v>
+        <v>1.380638670573015</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4442,7 +4442,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>28.23250334989863</v>
+        <v>27.40213560431338</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4450,22 +4450,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09125699037170804</v>
+        <v>0.09113727532338374</v>
       </c>
       <c r="C36">
-        <v>80.36362971767801</v>
+        <v>78.83163538057677</v>
       </c>
       <c r="D36">
-        <v>-81.57197028232197</v>
+        <v>-81.78736461942322</v>
       </c>
       <c r="E36">
-        <v>39.5044</v>
+        <v>40.82100000000001</v>
       </c>
       <c r="F36">
-        <v>44.7644</v>
+        <v>46.081</v>
       </c>
       <c r="G36">
         <v>206.7</v>
@@ -4486,28 +4486,28 @@
         <v>61.7</v>
       </c>
       <c r="M36">
-        <v>2.25164932</v>
+        <v>2.3178743</v>
       </c>
       <c r="N36">
-        <v>59.44835068</v>
+        <v>59.3821257</v>
       </c>
       <c r="O36">
-        <v>9.808977862200001</v>
+        <v>9.798050740500001</v>
       </c>
       <c r="P36">
-        <v>49.6393728178</v>
+        <v>49.5840749595</v>
       </c>
       <c r="Q36">
-        <v>51.6393728178</v>
+        <v>51.5840749595</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1166315460177395</v>
+        <v>0.1175955389590519</v>
       </c>
       <c r="T36">
-        <v>1.380638670573015</v>
+        <v>1.399428687278313</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4524,7 +4524,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>27.40213560431338</v>
+        <v>26.61921744419013</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4532,22 +4532,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09113727532338374</v>
+        <v>0.09101756027505942</v>
       </c>
       <c r="C37">
-        <v>78.83163538057677</v>
+        <v>77.29850051562227</v>
       </c>
       <c r="D37">
-        <v>-81.78736461942322</v>
+        <v>-82.00389948437773</v>
       </c>
       <c r="E37">
-        <v>40.82100000000001</v>
+        <v>42.13760000000001</v>
       </c>
       <c r="F37">
-        <v>46.081</v>
+        <v>47.3976</v>
       </c>
       <c r="G37">
         <v>206.7</v>
@@ -4568,28 +4568,28 @@
         <v>61.7</v>
       </c>
       <c r="M37">
-        <v>2.3178743</v>
+        <v>2.38409928</v>
       </c>
       <c r="N37">
-        <v>59.3821257</v>
+        <v>59.31590072</v>
       </c>
       <c r="O37">
-        <v>9.798050740500001</v>
+        <v>9.787123618800001</v>
       </c>
       <c r="P37">
-        <v>49.5840749595</v>
+        <v>49.5287771012</v>
       </c>
       <c r="Q37">
-        <v>51.5840749595</v>
+        <v>51.5287771012</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1175955389590519</v>
+        <v>0.1185896566797804</v>
       </c>
       <c r="T37">
-        <v>1.399428687278313</v>
+        <v>1.418805892005651</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>26.61921744419013</v>
+        <v>25.87979473740708</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4614,22 +4614,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09101756027505943</v>
+        <v>0.09089784522673512</v>
       </c>
       <c r="C38">
-        <v>77.29850051562228</v>
+        <v>75.76421604000714</v>
       </c>
       <c r="D38">
-        <v>-82.00389948437771</v>
+        <v>-82.22158395999284</v>
       </c>
       <c r="E38">
-        <v>42.1376</v>
+        <v>43.4542</v>
       </c>
       <c r="F38">
-        <v>47.3976</v>
+        <v>48.7142</v>
       </c>
       <c r="G38">
         <v>206.7</v>
@@ -4650,28 +4650,28 @@
         <v>61.7</v>
       </c>
       <c r="M38">
-        <v>2.38409928</v>
+        <v>2.45032426</v>
       </c>
       <c r="N38">
-        <v>59.31590072</v>
+        <v>59.24967574</v>
       </c>
       <c r="O38">
-        <v>9.787123618800001</v>
+        <v>9.776196497100001</v>
       </c>
       <c r="P38">
-        <v>49.5287771012</v>
+        <v>49.4734792429</v>
       </c>
       <c r="Q38">
-        <v>51.5287771012</v>
+        <v>51.4734792429</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1185896566797804</v>
+        <v>0.1196153336932304</v>
       </c>
       <c r="T38">
-        <v>1.418805892005651</v>
+        <v>1.438798246089412</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4688,7 +4688,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>25.87979473740708</v>
+        <v>25.18034082558527</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4696,22 +4696,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09089784522673512</v>
+        <v>0.09077813017841081</v>
       </c>
       <c r="C39">
-        <v>75.76421604000714</v>
+        <v>74.22877277422381</v>
       </c>
       <c r="D39">
-        <v>-82.22158395999284</v>
+        <v>-82.44042722577618</v>
       </c>
       <c r="E39">
-        <v>43.4542</v>
+        <v>44.7708</v>
       </c>
       <c r="F39">
-        <v>48.7142</v>
+        <v>50.0308</v>
       </c>
       <c r="G39">
         <v>206.7</v>
@@ -4732,28 +4732,28 @@
         <v>61.7</v>
       </c>
       <c r="M39">
-        <v>2.45032426</v>
+        <v>2.51654924</v>
       </c>
       <c r="N39">
-        <v>59.24967574</v>
+        <v>59.18345076</v>
       </c>
       <c r="O39">
-        <v>9.776196497100001</v>
+        <v>9.765269375400001</v>
       </c>
       <c r="P39">
-        <v>49.4734792429</v>
+        <v>49.4181813846</v>
       </c>
       <c r="Q39">
-        <v>51.4734792429</v>
+        <v>51.4181813846</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1196153336932304</v>
+        <v>0.1206740970619529</v>
       </c>
       <c r="T39">
-        <v>1.438798246089412</v>
+        <v>1.459435514821037</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4770,7 +4770,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>25.18034082558527</v>
+        <v>24.51770027754355</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4778,22 +4778,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09077813017841081</v>
+        <v>0.09065841513008649</v>
       </c>
       <c r="C40">
-        <v>74.22877277422381</v>
+        <v>72.6921614407741</v>
       </c>
       <c r="D40">
-        <v>-82.44042722577618</v>
+        <v>-82.6604385592259</v>
       </c>
       <c r="E40">
-        <v>44.7708</v>
+        <v>46.0874</v>
       </c>
       <c r="F40">
-        <v>50.0308</v>
+        <v>51.3474</v>
       </c>
       <c r="G40">
         <v>206.7</v>
@@ -4814,28 +4814,28 @@
         <v>61.7</v>
       </c>
       <c r="M40">
-        <v>2.51654924</v>
+        <v>2.58277422</v>
       </c>
       <c r="N40">
-        <v>59.18345076</v>
+        <v>59.11722578000001</v>
       </c>
       <c r="O40">
-        <v>9.765269375400001</v>
+        <v>9.754342253700001</v>
       </c>
       <c r="P40">
-        <v>49.4181813846</v>
+        <v>49.3628835263</v>
       </c>
       <c r="Q40">
-        <v>51.4181813846</v>
+        <v>51.3628835263</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1206740970619529</v>
+        <v>0.1217675739837484</v>
       </c>
       <c r="T40">
-        <v>1.459435514821037</v>
+        <v>1.480749415314354</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4852,7 +4852,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>24.51770027754355</v>
+        <v>23.88904129606808</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4860,22 +4860,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09065841513008649</v>
+        <v>0.09053870008176218</v>
       </c>
       <c r="C41">
-        <v>72.6921614407741</v>
+        <v>71.15437266285829</v>
       </c>
       <c r="D41">
-        <v>-82.6604385592259</v>
+        <v>-82.88162733714169</v>
       </c>
       <c r="E41">
-        <v>46.0874</v>
+        <v>47.404</v>
       </c>
       <c r="F41">
-        <v>51.3474</v>
+        <v>52.664</v>
       </c>
       <c r="G41">
         <v>206.7</v>
@@ -4896,28 +4896,28 @@
         <v>61.7</v>
       </c>
       <c r="M41">
-        <v>2.58277422</v>
+        <v>2.6489992</v>
       </c>
       <c r="N41">
-        <v>59.11722578000001</v>
+        <v>59.0510008</v>
       </c>
       <c r="O41">
-        <v>9.754342253700001</v>
+        <v>9.743415132000001</v>
       </c>
       <c r="P41">
-        <v>49.3628835263</v>
+        <v>49.307585668</v>
       </c>
       <c r="Q41">
-        <v>51.3628835263</v>
+        <v>51.307585668</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1217675739837484</v>
+        <v>0.1228975001362703</v>
       </c>
       <c r="T41">
-        <v>1.480749415314354</v>
+        <v>1.502773779157449</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4934,7 +4934,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>23.88904129606808</v>
+        <v>23.29181526366637</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4942,22 +4942,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09053870008176218</v>
+        <v>0.09041898503343787</v>
       </c>
       <c r="C42">
-        <v>71.15437266285829</v>
+        <v>69.61539696304291</v>
       </c>
       <c r="D42">
-        <v>-82.88162733714169</v>
+        <v>-83.10400303695708</v>
       </c>
       <c r="E42">
-        <v>47.404</v>
+        <v>48.7206</v>
       </c>
       <c r="F42">
-        <v>52.664</v>
+        <v>53.9806</v>
       </c>
       <c r="G42">
         <v>206.7</v>
@@ -4978,28 +4978,28 @@
         <v>61.7</v>
       </c>
       <c r="M42">
-        <v>2.6489992</v>
+        <v>2.71522418</v>
       </c>
       <c r="N42">
-        <v>59.0510008</v>
+        <v>58.98477582</v>
       </c>
       <c r="O42">
-        <v>9.743415132000001</v>
+        <v>9.732488010300001</v>
       </c>
       <c r="P42">
-        <v>49.307585668</v>
+        <v>49.2522878097</v>
       </c>
       <c r="Q42">
-        <v>51.307585668</v>
+        <v>51.2522878097</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1228975001362703</v>
+        <v>0.1240657288702337</v>
       </c>
       <c r="T42">
-        <v>1.502773779157449</v>
+        <v>1.525544731605394</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -5016,7 +5016,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>23.29181526366637</v>
+        <v>22.723722208455</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5024,22 +5024,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09041898503343787</v>
+        <v>0.09029926998511356</v>
       </c>
       <c r="C43">
-        <v>69.61539696304291</v>
+        <v>68.07522476190699</v>
       </c>
       <c r="D43">
-        <v>-83.10400303695708</v>
+        <v>-83.32757523809299</v>
       </c>
       <c r="E43">
-        <v>48.7206</v>
+        <v>50.03720000000001</v>
       </c>
       <c r="F43">
-        <v>53.9806</v>
+        <v>55.2972</v>
       </c>
       <c r="G43">
         <v>206.7</v>
@@ -5060,28 +5060,28 @@
         <v>61.7</v>
       </c>
       <c r="M43">
-        <v>2.71522418</v>
+        <v>2.78144916</v>
       </c>
       <c r="N43">
-        <v>58.98477582</v>
+        <v>58.91855084</v>
       </c>
       <c r="O43">
-        <v>9.732488010300001</v>
+        <v>9.721560888600001</v>
       </c>
       <c r="P43">
-        <v>49.2522878097</v>
+        <v>49.1969899514</v>
       </c>
       <c r="Q43">
-        <v>51.2522878097</v>
+        <v>51.1969899514</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1240657288702337</v>
+        <v>0.1252742413536441</v>
       </c>
       <c r="T43">
-        <v>1.525544731605394</v>
+        <v>1.549100889310165</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>22.723722208455</v>
+        <v>22.18268120349178</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5106,22 +5106,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09029926998511356</v>
+        <v>0.09017955493678925</v>
       </c>
       <c r="C44">
-        <v>68.07522476190701</v>
+        <v>66.53384637666667</v>
       </c>
       <c r="D44">
-        <v>-83.32757523809299</v>
+        <v>-83.55235362333332</v>
       </c>
       <c r="E44">
-        <v>50.0372</v>
+        <v>51.3538</v>
       </c>
       <c r="F44">
-        <v>55.2972</v>
+        <v>56.6138</v>
       </c>
       <c r="G44">
         <v>206.7</v>
@@ -5142,28 +5142,28 @@
         <v>61.7</v>
       </c>
       <c r="M44">
-        <v>2.78144916</v>
+        <v>2.84767414</v>
       </c>
       <c r="N44">
-        <v>58.91855084</v>
+        <v>58.85232586</v>
       </c>
       <c r="O44">
-        <v>9.721560888600001</v>
+        <v>9.710633766900001</v>
       </c>
       <c r="P44">
-        <v>49.1969899514</v>
+        <v>49.1416920931</v>
       </c>
       <c r="Q44">
-        <v>51.1969899514</v>
+        <v>51.1416920931</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1252742413536441</v>
+        <v>0.1265251577838408</v>
       </c>
       <c r="T44">
-        <v>1.549100889310165</v>
+        <v>1.573483578864226</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -5180,7 +5180,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>22.18268120349178</v>
+        <v>21.66680489643383</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5188,22 +5188,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09017955493678925</v>
+        <v>0.09005983988846492</v>
       </c>
       <c r="C45">
-        <v>66.53384637666667</v>
+        <v>64.99125201977708</v>
       </c>
       <c r="D45">
-        <v>-83.55235362333332</v>
+        <v>-83.77834798022292</v>
       </c>
       <c r="E45">
-        <v>51.3538</v>
+        <v>52.6704</v>
       </c>
       <c r="F45">
-        <v>56.6138</v>
+        <v>57.9304</v>
       </c>
       <c r="G45">
         <v>206.7</v>
@@ -5224,28 +5224,28 @@
         <v>61.7</v>
       </c>
       <c r="M45">
-        <v>2.84767414</v>
+        <v>2.91389912</v>
       </c>
       <c r="N45">
-        <v>58.85232586</v>
+        <v>58.78610088000001</v>
       </c>
       <c r="O45">
-        <v>9.710633766900001</v>
+        <v>9.699706645200001</v>
       </c>
       <c r="P45">
-        <v>49.1416920931</v>
+        <v>49.0863942348</v>
       </c>
       <c r="Q45">
-        <v>51.1416920931</v>
+        <v>51.0863942348</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1265251577838408</v>
+        <v>0.1278207498008302</v>
       </c>
       <c r="T45">
-        <v>1.573483578864226</v>
+        <v>1.598737078759503</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -5262,7 +5262,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>21.66680489643383</v>
+        <v>21.17437751242397</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5270,22 +5270,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09005983988846492</v>
+        <v>0.08994012484014063</v>
       </c>
       <c r="C46">
-        <v>64.99125201977708</v>
+        <v>63.4474317975121</v>
       </c>
       <c r="D46">
-        <v>-83.77834798022292</v>
+        <v>-84.00556820248789</v>
       </c>
       <c r="E46">
-        <v>52.6704</v>
+        <v>53.987</v>
       </c>
       <c r="F46">
-        <v>57.9304</v>
+        <v>59.247</v>
       </c>
       <c r="G46">
         <v>206.7</v>
@@ -5306,28 +5306,28 @@
         <v>61.7</v>
       </c>
       <c r="M46">
-        <v>2.91389912</v>
+        <v>2.9801241</v>
       </c>
       <c r="N46">
-        <v>58.78610088000001</v>
+        <v>58.71987590000001</v>
       </c>
       <c r="O46">
-        <v>9.699706645200001</v>
+        <v>9.688779523500001</v>
       </c>
       <c r="P46">
-        <v>49.0863942348</v>
+        <v>49.0310963765</v>
       </c>
       <c r="Q46">
-        <v>51.0863942348</v>
+        <v>51.0310963765</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1278207498008302</v>
+        <v>0.1291634542548011</v>
       </c>
       <c r="T46">
-        <v>1.598737078759503</v>
+        <v>1.624908887741882</v>
       </c>
       <c r="U46">
         <v>0.0503</v>
@@ -5344,7 +5344,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>21.17437751242397</v>
+        <v>20.70383578992566</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5352,22 +5352,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08994012484014063</v>
+        <v>0.08982040979181632</v>
       </c>
       <c r="C47">
-        <v>63.4474317975121</v>
+        <v>61.90237570851991</v>
       </c>
       <c r="D47">
-        <v>-84.00556820248789</v>
+        <v>-84.23402429148008</v>
       </c>
       <c r="E47">
-        <v>53.987</v>
+        <v>55.3036</v>
       </c>
       <c r="F47">
-        <v>59.247</v>
+        <v>60.5636</v>
       </c>
       <c r="G47">
         <v>206.7</v>
@@ -5388,28 +5388,28 @@
         <v>61.7</v>
       </c>
       <c r="M47">
-        <v>2.9801241</v>
+        <v>3.04634908</v>
       </c>
       <c r="N47">
-        <v>58.71987590000001</v>
+        <v>58.65365092</v>
       </c>
       <c r="O47">
-        <v>9.688779523500001</v>
+        <v>9.677852401800001</v>
       </c>
       <c r="P47">
-        <v>49.0310963765</v>
+        <v>48.9757985182</v>
       </c>
       <c r="Q47">
-        <v>51.0310963765</v>
+        <v>50.9757985182</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1291634542548011</v>
+        <v>0.1305558885033636</v>
       </c>
       <c r="T47">
-        <v>1.624908887741882</v>
+        <v>1.652050022982868</v>
       </c>
       <c r="U47">
         <v>0.0503</v>
@@ -5426,7 +5426,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>20.70383578992566</v>
+        <v>20.25375240318815</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5434,22 +5434,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08982040979181632</v>
+        <v>0.089700694743492</v>
       </c>
       <c r="C48">
-        <v>61.90237570851991</v>
+        <v>60.35607364235609</v>
       </c>
       <c r="D48">
-        <v>-84.23402429148008</v>
+        <v>-84.46372635764389</v>
       </c>
       <c r="E48">
-        <v>55.3036</v>
+        <v>56.6202</v>
       </c>
       <c r="F48">
-        <v>60.5636</v>
+        <v>61.8802</v>
       </c>
       <c r="G48">
         <v>206.7</v>
@@ -5470,28 +5470,28 @@
         <v>61.7</v>
       </c>
       <c r="M48">
-        <v>3.04634908</v>
+        <v>3.11257406</v>
       </c>
       <c r="N48">
-        <v>58.65365092</v>
+        <v>58.58742594</v>
       </c>
       <c r="O48">
-        <v>9.677852401800001</v>
+        <v>9.666925280100001</v>
       </c>
       <c r="P48">
-        <v>48.9757985182</v>
+        <v>48.9205006599</v>
       </c>
       <c r="Q48">
-        <v>50.9757985182</v>
+        <v>50.9205006599</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1305558885033636</v>
+        <v>0.132000867440551</v>
       </c>
       <c r="T48">
-        <v>1.652050022982868</v>
+        <v>1.680215352006531</v>
       </c>
       <c r="U48">
         <v>0.0503</v>
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>20.25375240318815</v>
+        <v>19.82282150099266</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5516,22 +5516,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.089700694743492</v>
+        <v>0.08958097969516769</v>
       </c>
       <c r="C49">
-        <v>60.35607364235609</v>
+        <v>58.80851537799199</v>
       </c>
       <c r="D49">
-        <v>-84.46372635764389</v>
+        <v>-84.694684622008</v>
       </c>
       <c r="E49">
-        <v>56.6202</v>
+        <v>57.93680000000001</v>
       </c>
       <c r="F49">
-        <v>61.8802</v>
+        <v>63.1968</v>
       </c>
       <c r="G49">
         <v>206.7</v>
@@ -5552,28 +5552,28 @@
         <v>61.7</v>
       </c>
       <c r="M49">
-        <v>3.11257406</v>
+        <v>3.17879904</v>
       </c>
       <c r="N49">
-        <v>58.58742594</v>
+        <v>58.52120096</v>
       </c>
       <c r="O49">
-        <v>9.666925280100001</v>
+        <v>9.655998158400001</v>
       </c>
       <c r="P49">
-        <v>48.9205006599</v>
+        <v>48.8652028016</v>
       </c>
       <c r="Q49">
-        <v>50.9205006599</v>
+        <v>50.8652028016</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.132000867440551</v>
+        <v>0.1335014224907071</v>
       </c>
       <c r="T49">
-        <v>1.680215352006531</v>
+        <v>1.709463962915721</v>
       </c>
       <c r="U49">
         <v>0.0503</v>
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>19.82282150099266</v>
+        <v>19.40984605305531</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5598,22 +5598,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08958097969516769</v>
+        <v>0.08946126464684337</v>
       </c>
       <c r="C50">
-        <v>58.80851537799199</v>
+        <v>57.2596905822984</v>
       </c>
       <c r="D50">
-        <v>-84.694684622008</v>
+        <v>-84.92690941770159</v>
       </c>
       <c r="E50">
-        <v>57.9368</v>
+        <v>59.25339999999999</v>
       </c>
       <c r="F50">
-        <v>63.1968</v>
+        <v>64.51339999999999</v>
       </c>
       <c r="G50">
         <v>206.7</v>
@@ -5634,28 +5634,28 @@
         <v>61.7</v>
       </c>
       <c r="M50">
-        <v>3.178799039999999</v>
+        <v>3.245024019999999</v>
       </c>
       <c r="N50">
-        <v>58.52120096</v>
+        <v>58.45497598</v>
       </c>
       <c r="O50">
-        <v>9.655998158400001</v>
+        <v>9.645071036700001</v>
       </c>
       <c r="P50">
-        <v>48.8652028016</v>
+        <v>48.8099049433</v>
       </c>
       <c r="Q50">
-        <v>50.8652028016</v>
+        <v>50.8099049433</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1335014224907071</v>
+        <v>0.1350608228369478</v>
       </c>
       <c r="T50">
-        <v>1.709463962915721</v>
+        <v>1.73985957817429</v>
       </c>
       <c r="U50">
         <v>0.0503</v>
@@ -5672,7 +5672,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>19.40984605305531</v>
+        <v>19.0137267458501</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5680,22 +5680,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08946126464684337</v>
+        <v>0.08934154959851906</v>
       </c>
       <c r="C51">
-        <v>57.2596905822984</v>
+        <v>55.70958880850483</v>
       </c>
       <c r="D51">
-        <v>-84.92690941770159</v>
+        <v>-85.16041119149516</v>
       </c>
       <c r="E51">
-        <v>59.25339999999999</v>
+        <v>60.57</v>
       </c>
       <c r="F51">
-        <v>64.51339999999999</v>
+        <v>65.83</v>
       </c>
       <c r="G51">
         <v>206.7</v>
@@ -5716,28 +5716,28 @@
         <v>61.7</v>
       </c>
       <c r="M51">
-        <v>3.245024019999999</v>
+        <v>3.311249</v>
       </c>
       <c r="N51">
-        <v>58.45497598</v>
+        <v>58.38875100000001</v>
       </c>
       <c r="O51">
-        <v>9.645071036700001</v>
+        <v>9.634143915000001</v>
       </c>
       <c r="P51">
-        <v>48.8099049433</v>
+        <v>48.754607085</v>
       </c>
       <c r="Q51">
-        <v>50.8099049433</v>
+        <v>50.754607085</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1350608228369478</v>
+        <v>0.1366825991970381</v>
       </c>
       <c r="T51">
-        <v>1.73985957817429</v>
+        <v>1.771471018043203</v>
       </c>
       <c r="U51">
         <v>0.0503</v>
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>19.0137267458501</v>
+        <v>18.6334522109331</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5762,22 +5762,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08934154959851906</v>
+        <v>0.08922183455019475</v>
       </c>
       <c r="C52">
-        <v>55.70958880850483</v>
+        <v>54.15819949463274</v>
       </c>
       <c r="D52">
-        <v>-85.16041119149516</v>
+        <v>-85.39520050536724</v>
       </c>
       <c r="E52">
-        <v>60.57</v>
+        <v>61.88660000000001</v>
       </c>
       <c r="F52">
-        <v>65.83</v>
+        <v>67.14660000000001</v>
       </c>
       <c r="G52">
         <v>206.7</v>
@@ -5798,28 +5798,28 @@
         <v>61.7</v>
       </c>
       <c r="M52">
-        <v>3.311249</v>
+        <v>3.37747398</v>
       </c>
       <c r="N52">
-        <v>58.38875100000001</v>
+        <v>58.32252602000001</v>
       </c>
       <c r="O52">
-        <v>9.634143915000001</v>
+        <v>9.623216793300001</v>
       </c>
       <c r="P52">
-        <v>48.754607085</v>
+        <v>48.6993092267</v>
       </c>
       <c r="Q52">
-        <v>50.754607085</v>
+        <v>50.6993092267</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1366825991970381</v>
+        <v>0.1383705705106015</v>
       </c>
       <c r="T52">
-        <v>1.771471018043203</v>
+        <v>1.804372720763907</v>
       </c>
       <c r="U52">
         <v>0.0503</v>
@@ -5836,7 +5836,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>18.6334522109331</v>
+        <v>18.26809040287559</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5844,22 +5844,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08922183455019475</v>
+        <v>0.08910211950187044</v>
       </c>
       <c r="C53">
-        <v>54.15819949463274</v>
+        <v>52.60551196190302</v>
       </c>
       <c r="D53">
-        <v>-85.39520050536724</v>
+        <v>-85.63128803809697</v>
       </c>
       <c r="E53">
-        <v>61.88660000000001</v>
+        <v>63.2032</v>
       </c>
       <c r="F53">
-        <v>67.14660000000001</v>
+        <v>68.4632</v>
       </c>
       <c r="G53">
         <v>206.7</v>
@@ -5880,28 +5880,28 @@
         <v>61.7</v>
       </c>
       <c r="M53">
-        <v>3.37747398</v>
+        <v>3.44369896</v>
       </c>
       <c r="N53">
-        <v>58.32252602000001</v>
+        <v>58.25630104</v>
       </c>
       <c r="O53">
-        <v>9.623216793300001</v>
+        <v>9.612289671600001</v>
       </c>
       <c r="P53">
-        <v>48.6993092267</v>
+        <v>48.6440113684</v>
       </c>
       <c r="Q53">
-        <v>50.6993092267</v>
+        <v>50.6440113684</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1383705705106015</v>
+        <v>0.1401288739622301</v>
       </c>
       <c r="T53">
-        <v>1.804372720763907</v>
+        <v>1.838645327764641</v>
       </c>
       <c r="U53">
         <v>0.0503</v>
@@ -5918,7 +5918,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>18.26809040287559</v>
+        <v>17.91678097205105</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5926,22 +5926,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08910211950187044</v>
+        <v>0.08898240445354612</v>
       </c>
       <c r="C54">
-        <v>52.60551196190302</v>
+        <v>51.05151541311697</v>
       </c>
       <c r="D54">
-        <v>-85.63128803809697</v>
+        <v>-85.86868458688301</v>
       </c>
       <c r="E54">
-        <v>63.2032</v>
+        <v>64.5198</v>
       </c>
       <c r="F54">
-        <v>68.4632</v>
+        <v>69.77980000000001</v>
       </c>
       <c r="G54">
         <v>206.7</v>
@@ -5962,28 +5962,28 @@
         <v>61.7</v>
       </c>
       <c r="M54">
-        <v>3.44369896</v>
+        <v>3.50992394</v>
       </c>
       <c r="N54">
-        <v>58.25630104</v>
+        <v>58.19007606</v>
       </c>
       <c r="O54">
-        <v>9.612289671600001</v>
+        <v>9.601362549900001</v>
       </c>
       <c r="P54">
-        <v>48.6440113684</v>
+        <v>48.5887135101</v>
       </c>
       <c r="Q54">
-        <v>50.6440113684</v>
+        <v>50.5887135101</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1401288739622301</v>
+        <v>0.1419619988373322</v>
       </c>
       <c r="T54">
-        <v>1.838645327764641</v>
+        <v>1.874376343573917</v>
       </c>
       <c r="U54">
         <v>0.0503</v>
@@ -6000,7 +6000,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>17.91678097205105</v>
+        <v>17.57872850088028</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6008,22 +6008,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08898240445354612</v>
+        <v>0.08886268940522181</v>
       </c>
       <c r="C55">
-        <v>51.05151541311697</v>
+        <v>49.49619893101038</v>
       </c>
       <c r="D55">
-        <v>-85.86868458688301</v>
+        <v>-86.1074010689896</v>
       </c>
       <c r="E55">
-        <v>64.5198</v>
+        <v>65.8364</v>
       </c>
       <c r="F55">
-        <v>69.77980000000001</v>
+        <v>71.0964</v>
       </c>
       <c r="G55">
         <v>206.7</v>
@@ -6044,28 +6044,28 @@
         <v>61.7</v>
       </c>
       <c r="M55">
-        <v>3.50992394</v>
+        <v>3.57614892</v>
       </c>
       <c r="N55">
-        <v>58.19007606</v>
+        <v>58.12385108</v>
       </c>
       <c r="O55">
-        <v>9.601362549900001</v>
+        <v>9.590435428200001</v>
       </c>
       <c r="P55">
-        <v>48.5887135101</v>
+        <v>48.5334156518</v>
       </c>
       <c r="Q55">
-        <v>50.5887135101</v>
+        <v>50.5334156518</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1419619988373322</v>
+        <v>0.1438748247939605</v>
       </c>
       <c r="T55">
-        <v>1.874376343573917</v>
+        <v>1.911660881809683</v>
       </c>
       <c r="U55">
         <v>0.0503</v>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>17.57872850088028</v>
+        <v>17.25319649160472</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6090,22 +6090,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08886268940522181</v>
+        <v>0.0887429743568975</v>
       </c>
       <c r="C56">
-        <v>49.49619893101038</v>
+        <v>47.93955147657969</v>
       </c>
       <c r="D56">
-        <v>-86.1074010689896</v>
+        <v>-86.34744852342028</v>
       </c>
       <c r="E56">
-        <v>65.8364</v>
+        <v>67.15300000000001</v>
       </c>
       <c r="F56">
-        <v>71.0964</v>
+        <v>72.41300000000001</v>
       </c>
       <c r="G56">
         <v>206.7</v>
@@ -6126,28 +6126,28 @@
         <v>61.7</v>
       </c>
       <c r="M56">
-        <v>3.57614892</v>
+        <v>3.6423739</v>
       </c>
       <c r="N56">
-        <v>58.12385108</v>
+        <v>58.0576261</v>
       </c>
       <c r="O56">
-        <v>9.590435428200001</v>
+        <v>9.579508306500001</v>
       </c>
       <c r="P56">
-        <v>48.5334156518</v>
+        <v>48.4781177935</v>
       </c>
       <c r="Q56">
-        <v>50.5334156518</v>
+        <v>50.4781177935</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1438748247939605</v>
+        <v>0.14587266523755</v>
       </c>
       <c r="T56">
-        <v>1.911660881809683</v>
+        <v>1.950602510633705</v>
       </c>
       <c r="U56">
         <v>0.0503</v>
@@ -6164,7 +6164,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>17.25319649160472</v>
+        <v>16.93950200993918</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6172,22 +6172,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.0887429743568975</v>
+        <v>0.08862325930857318</v>
       </c>
       <c r="C57">
-        <v>47.93955147657969</v>
+        <v>46.3815618873806</v>
       </c>
       <c r="D57">
-        <v>-86.34744852342028</v>
+        <v>-86.58883811261938</v>
       </c>
       <c r="E57">
-        <v>67.15300000000001</v>
+        <v>68.4696</v>
       </c>
       <c r="F57">
-        <v>72.41300000000001</v>
+        <v>73.7296</v>
       </c>
       <c r="G57">
         <v>206.7</v>
@@ -6208,28 +6208,28 @@
         <v>61.7</v>
       </c>
       <c r="M57">
-        <v>3.6423739</v>
+        <v>3.70859888</v>
       </c>
       <c r="N57">
-        <v>58.0576261</v>
+        <v>57.99140112000001</v>
       </c>
       <c r="O57">
-        <v>9.579508306500001</v>
+        <v>9.568581184800001</v>
       </c>
       <c r="P57">
-        <v>48.4781177935</v>
+        <v>48.4228199352</v>
       </c>
       <c r="Q57">
-        <v>50.4781177935</v>
+        <v>50.4228199352</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.14587266523755</v>
+        <v>0.1479613166103936</v>
       </c>
       <c r="T57">
-        <v>1.950602510633705</v>
+        <v>1.991314213495183</v>
       </c>
       <c r="U57">
         <v>0.0503</v>
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>16.93950200993918</v>
+        <v>16.63701090261883</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6254,22 +6254,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08862325930857318</v>
+        <v>0.08850354426024887</v>
       </c>
       <c r="C58">
-        <v>46.3815618873806</v>
+        <v>44.82221887579766</v>
       </c>
       <c r="D58">
-        <v>-86.58883811261938</v>
+        <v>-86.83158112420232</v>
       </c>
       <c r="E58">
-        <v>68.4696</v>
+        <v>69.78620000000001</v>
       </c>
       <c r="F58">
-        <v>73.7296</v>
+        <v>75.04620000000001</v>
       </c>
       <c r="G58">
         <v>206.7</v>
@@ -6290,28 +6290,28 @@
         <v>61.7</v>
       </c>
       <c r="M58">
-        <v>3.70859888</v>
+        <v>3.774823860000001</v>
       </c>
       <c r="N58">
-        <v>57.99140112000001</v>
+        <v>57.92517614</v>
       </c>
       <c r="O58">
-        <v>9.568581184800001</v>
+        <v>9.557654063100001</v>
       </c>
       <c r="P58">
-        <v>48.4228199352</v>
+        <v>48.3675220769</v>
       </c>
       <c r="Q58">
-        <v>50.4228199352</v>
+        <v>50.3675220769</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1479613166103936</v>
+        <v>0.1501471145587183</v>
       </c>
       <c r="T58">
-        <v>1.991314213495183</v>
+        <v>2.033919483931613</v>
       </c>
       <c r="U58">
         <v>0.0503</v>
@@ -6328,7 +6328,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>16.63701090261883</v>
+        <v>16.34513351836236</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6336,22 +6336,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08850354426024887</v>
+        <v>0.08838382921192456</v>
       </c>
       <c r="C59">
-        <v>44.82221887579766</v>
+        <v>43.26151102728484</v>
       </c>
       <c r="D59">
-        <v>-86.83158112420232</v>
+        <v>-87.07568897271514</v>
       </c>
       <c r="E59">
-        <v>69.78620000000001</v>
+        <v>71.1028</v>
       </c>
       <c r="F59">
-        <v>75.04620000000001</v>
+        <v>76.36280000000001</v>
       </c>
       <c r="G59">
         <v>206.7</v>
@@ -6372,28 +6372,28 @@
         <v>61.7</v>
       </c>
       <c r="M59">
-        <v>3.774823860000001</v>
+        <v>3.84104884</v>
       </c>
       <c r="N59">
-        <v>57.92517614</v>
+        <v>57.85895116</v>
       </c>
       <c r="O59">
-        <v>9.557654063100001</v>
+        <v>9.546726941400001</v>
       </c>
       <c r="P59">
-        <v>48.3675220769</v>
+        <v>48.3122242186</v>
       </c>
       <c r="Q59">
-        <v>50.3675220769</v>
+        <v>50.3122242186</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1501471145587183</v>
+        <v>0.1524369981236299</v>
       </c>
       <c r="T59">
-        <v>2.033919483931613</v>
+        <v>2.078553576769778</v>
       </c>
       <c r="U59">
         <v>0.0503</v>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>16.34513351836236</v>
+        <v>16.06332087149405</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6418,22 +6418,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08838382921192456</v>
+        <v>0.08826411416360025</v>
       </c>
       <c r="C60">
-        <v>43.26151102728485</v>
+        <v>41.69942679857637</v>
       </c>
       <c r="D60">
-        <v>-87.07568897271514</v>
+        <v>-87.32117320142363</v>
       </c>
       <c r="E60">
-        <v>71.10279999999999</v>
+        <v>72.41939999999998</v>
       </c>
       <c r="F60">
-        <v>76.36279999999999</v>
+        <v>77.67939999999999</v>
       </c>
       <c r="G60">
         <v>206.7</v>
@@ -6454,28 +6454,28 @@
         <v>61.7</v>
       </c>
       <c r="M60">
-        <v>3.84104884</v>
+        <v>3.907273819999999</v>
       </c>
       <c r="N60">
-        <v>57.85895116</v>
+        <v>57.79272618</v>
       </c>
       <c r="O60">
-        <v>9.546726941400001</v>
+        <v>9.535799819700001</v>
       </c>
       <c r="P60">
-        <v>48.3122242186</v>
+        <v>48.2569263603</v>
       </c>
       <c r="Q60">
-        <v>50.3122242186</v>
+        <v>50.2569263603</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1524369981236299</v>
+        <v>0.1548385833258543</v>
       </c>
       <c r="T60">
-        <v>2.078553576769778</v>
+        <v>2.125364942429317</v>
       </c>
       <c r="U60">
         <v>0.0503</v>
@@ -6492,7 +6492,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>16.06332087149405</v>
+        <v>15.79106119570602</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6500,22 +6500,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08826411416360025</v>
+        <v>0.08814439911527593</v>
       </c>
       <c r="C61">
-        <v>41.69942679857637</v>
+        <v>40.13595451586698</v>
       </c>
       <c r="D61">
-        <v>-87.32117320142363</v>
+        <v>-87.56804548413301</v>
       </c>
       <c r="E61">
-        <v>72.41939999999998</v>
+        <v>73.73599999999999</v>
       </c>
       <c r="F61">
-        <v>77.67939999999999</v>
+        <v>78.996</v>
       </c>
       <c r="G61">
         <v>206.7</v>
@@ -6536,28 +6536,28 @@
         <v>61.7</v>
       </c>
       <c r="M61">
-        <v>3.907273819999999</v>
+        <v>3.9734988</v>
       </c>
       <c r="N61">
-        <v>57.79272618</v>
+        <v>57.7265012</v>
       </c>
       <c r="O61">
-        <v>9.535799819700001</v>
+        <v>9.524872698000001</v>
       </c>
       <c r="P61">
-        <v>48.2569263603</v>
+        <v>48.201628502</v>
       </c>
       <c r="Q61">
-        <v>50.2569263603</v>
+        <v>50.201628502</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1548385833258543</v>
+        <v>0.1573602477881898</v>
       </c>
       <c r="T61">
-        <v>2.125364942429317</v>
+        <v>2.174516876371833</v>
       </c>
       <c r="U61">
         <v>0.0503</v>
@@ -6574,7 +6574,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>15.79106119570602</v>
+        <v>15.52787684244425</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6582,22 +6582,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08814439911527593</v>
+        <v>0.08802468406695163</v>
       </c>
       <c r="C62">
-        <v>40.13595451586698</v>
+        <v>38.57108237296178</v>
       </c>
       <c r="D62">
-        <v>-87.56804548413301</v>
+        <v>-87.81631762703822</v>
       </c>
       <c r="E62">
-        <v>73.73599999999999</v>
+        <v>75.05259999999998</v>
       </c>
       <c r="F62">
-        <v>78.996</v>
+        <v>80.31259999999999</v>
       </c>
       <c r="G62">
         <v>206.7</v>
@@ -6618,28 +6618,28 @@
         <v>61.7</v>
       </c>
       <c r="M62">
-        <v>3.9734988</v>
+        <v>4.039723779999999</v>
       </c>
       <c r="N62">
-        <v>57.7265012</v>
+        <v>57.66027622</v>
       </c>
       <c r="O62">
-        <v>9.524872698000001</v>
+        <v>9.513945576300001</v>
       </c>
       <c r="P62">
-        <v>48.201628502</v>
+        <v>48.1463306437</v>
       </c>
       <c r="Q62">
-        <v>50.201628502</v>
+        <v>50.1463306437</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1573602477881898</v>
+        <v>0.160011228376799</v>
       </c>
       <c r="T62">
-        <v>2.174516876371833</v>
+        <v>2.226189422311401</v>
       </c>
       <c r="U62">
         <v>0.0503</v>
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>15.52787684244425</v>
+        <v>15.27332148437139</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6664,22 +6664,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08802468406695163</v>
+        <v>0.08790496901862731</v>
       </c>
       <c r="C63">
-        <v>38.57108237296178</v>
+        <v>37.00479842939365</v>
       </c>
       <c r="D63">
-        <v>-87.81631762703822</v>
+        <v>-88.06600157060635</v>
       </c>
       <c r="E63">
-        <v>75.05259999999998</v>
+        <v>76.36919999999999</v>
       </c>
       <c r="F63">
-        <v>80.31259999999999</v>
+        <v>81.6292</v>
       </c>
       <c r="G63">
         <v>206.7</v>
@@ -6700,28 +6700,28 @@
         <v>61.7</v>
       </c>
       <c r="M63">
-        <v>4.039723779999999</v>
+        <v>4.10594876</v>
       </c>
       <c r="N63">
-        <v>57.66027622</v>
+        <v>57.59405124000001</v>
       </c>
       <c r="O63">
-        <v>9.513945576300001</v>
+        <v>9.503018454600001</v>
       </c>
       <c r="P63">
-        <v>48.1463306437</v>
+        <v>48.0910327854</v>
       </c>
       <c r="Q63">
-        <v>50.1463306437</v>
+        <v>50.0910327854</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.160011228376799</v>
+        <v>0.1628017342595456</v>
       </c>
       <c r="T63">
-        <v>2.226189422311401</v>
+        <v>2.280581575931999</v>
       </c>
       <c r="U63">
         <v>0.0503</v>
@@ -6738,7 +6738,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>15.27332148437139</v>
+        <v>15.02697758946218</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6746,22 +6746,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08790496901862731</v>
+        <v>0.087785253970303</v>
       </c>
       <c r="C64">
-        <v>37.00479842939365</v>
+        <v>35.43709060850941</v>
       </c>
       <c r="D64">
-        <v>-88.06600157060635</v>
+        <v>-88.31710939149058</v>
       </c>
       <c r="E64">
-        <v>76.36919999999999</v>
+        <v>77.6858</v>
       </c>
       <c r="F64">
-        <v>81.6292</v>
+        <v>82.94580000000001</v>
       </c>
       <c r="G64">
         <v>206.7</v>
@@ -6782,28 +6782,28 @@
         <v>61.7</v>
       </c>
       <c r="M64">
-        <v>4.10594876</v>
+        <v>4.17217374</v>
       </c>
       <c r="N64">
-        <v>57.59405124000001</v>
+        <v>57.52782626</v>
       </c>
       <c r="O64">
-        <v>9.503018454600001</v>
+        <v>9.492091332900001</v>
       </c>
       <c r="P64">
-        <v>48.0910327854</v>
+        <v>48.0357349271</v>
       </c>
       <c r="Q64">
-        <v>50.0910327854</v>
+        <v>50.0357349271</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1628017342595456</v>
+        <v>0.1657430782981162</v>
       </c>
       <c r="T64">
-        <v>2.280581575931999</v>
+        <v>2.337913845964521</v>
       </c>
       <c r="U64">
         <v>0.0503</v>
@@ -6820,7 +6820,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>15.02697758946218</v>
+        <v>14.78845413566119</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6828,22 +6828,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.087785253970303</v>
+        <v>0.0876655389219787</v>
       </c>
       <c r="C65">
-        <v>35.43709060850941</v>
+        <v>33.86794669552245</v>
       </c>
       <c r="D65">
-        <v>-88.31710939149058</v>
+        <v>-88.56965330447754</v>
       </c>
       <c r="E65">
-        <v>77.6858</v>
+        <v>79.00239999999999</v>
       </c>
       <c r="F65">
-        <v>82.94580000000001</v>
+        <v>84.2624</v>
       </c>
       <c r="G65">
         <v>206.7</v>
@@ -6864,28 +6864,28 @@
         <v>61.7</v>
       </c>
       <c r="M65">
-        <v>4.17217374</v>
+        <v>4.23839872</v>
       </c>
       <c r="N65">
-        <v>57.52782626</v>
+        <v>57.46160128</v>
       </c>
       <c r="O65">
-        <v>9.492091332900001</v>
+        <v>9.481164211200001</v>
       </c>
       <c r="P65">
-        <v>48.0357349271</v>
+        <v>47.9804370688</v>
       </c>
       <c r="Q65">
-        <v>50.0357349271</v>
+        <v>49.9804370688</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1657430782981162</v>
+        <v>0.1688478303388297</v>
       </c>
       <c r="T65">
-        <v>2.337913845964521</v>
+        <v>2.398431242109961</v>
       </c>
       <c r="U65">
         <v>0.0503</v>
@@ -6902,7 +6902,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>14.78845413566119</v>
+        <v>14.55738453979148</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6910,22 +6910,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.0876655389219787</v>
+        <v>0.08754582387365438</v>
       </c>
       <c r="C66">
-        <v>33.86794669552245</v>
+        <v>32.29735433553202</v>
       </c>
       <c r="D66">
-        <v>-88.56965330447754</v>
+        <v>-88.82364566446796</v>
       </c>
       <c r="E66">
-        <v>79.00239999999999</v>
+        <v>80.319</v>
       </c>
       <c r="F66">
-        <v>84.2624</v>
+        <v>85.57900000000001</v>
       </c>
       <c r="G66">
         <v>206.7</v>
@@ -6946,28 +6946,28 @@
         <v>61.7</v>
       </c>
       <c r="M66">
-        <v>4.23839872</v>
+        <v>4.3046237</v>
       </c>
       <c r="N66">
-        <v>57.46160128</v>
+        <v>57.3953763</v>
       </c>
       <c r="O66">
-        <v>9.481164211200001</v>
+        <v>9.470237089500001</v>
       </c>
       <c r="P66">
-        <v>47.9804370688</v>
+        <v>47.9251392105</v>
       </c>
       <c r="Q66">
-        <v>49.9804370688</v>
+        <v>49.9251392105</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1688478303388297</v>
+        <v>0.1721299967818697</v>
       </c>
       <c r="T66">
-        <v>2.398431242109961</v>
+        <v>2.462406775177998</v>
       </c>
       <c r="U66">
         <v>0.0503</v>
@@ -6984,7 +6984,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>14.55738453979148</v>
+        <v>14.33342477764084</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6992,22 +6992,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.08754582387365438</v>
+        <v>0.08742610882533007</v>
       </c>
       <c r="C67">
-        <v>32.29735433553202</v>
+        <v>30.72530103150874</v>
       </c>
       <c r="D67">
-        <v>-88.82364566446796</v>
+        <v>-89.07909896849125</v>
       </c>
       <c r="E67">
-        <v>80.319</v>
+        <v>81.6356</v>
       </c>
       <c r="F67">
-        <v>85.57900000000001</v>
+        <v>86.8956</v>
       </c>
       <c r="G67">
         <v>206.7</v>
@@ -7028,28 +7028,28 @@
         <v>61.7</v>
       </c>
       <c r="M67">
-        <v>4.3046237</v>
+        <v>4.37084868</v>
       </c>
       <c r="N67">
-        <v>57.3953763</v>
+        <v>57.32915132</v>
       </c>
       <c r="O67">
-        <v>9.470237089500001</v>
+        <v>9.459309967800001</v>
       </c>
       <c r="P67">
-        <v>47.9251392105</v>
+        <v>47.8698413522</v>
       </c>
       <c r="Q67">
-        <v>49.9251392105</v>
+        <v>49.8698413522</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1721299967818697</v>
+        <v>0.1756052318392061</v>
       </c>
       <c r="T67">
-        <v>2.462406775177998</v>
+        <v>2.530145574897095</v>
       </c>
       <c r="U67">
         <v>0.0503</v>
@@ -7066,7 +7066,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>14.33342477764084</v>
+        <v>14.11625167494931</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7074,22 +7074,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.08742610882533007</v>
+        <v>0.08730639377700575</v>
       </c>
       <c r="C68">
-        <v>30.72530103150874</v>
+        <v>29.15177414224456</v>
       </c>
       <c r="D68">
-        <v>-89.07909896849125</v>
+        <v>-89.33602585775542</v>
       </c>
       <c r="E68">
-        <v>81.6356</v>
+        <v>82.9522</v>
       </c>
       <c r="F68">
-        <v>86.8956</v>
+        <v>88.21220000000001</v>
       </c>
       <c r="G68">
         <v>206.7</v>
@@ -7110,28 +7110,28 @@
         <v>61.7</v>
       </c>
       <c r="M68">
-        <v>4.37084868</v>
+        <v>4.43707366</v>
       </c>
       <c r="N68">
-        <v>57.32915132</v>
+        <v>57.26292634</v>
       </c>
       <c r="O68">
-        <v>9.459309967800001</v>
+        <v>9.448382846100001</v>
       </c>
       <c r="P68">
-        <v>47.8698413522</v>
+        <v>47.8145434939</v>
       </c>
       <c r="Q68">
-        <v>49.8698413522</v>
+        <v>49.8145434939</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1756052318392061</v>
+        <v>0.1792910872030478</v>
       </c>
       <c r="T68">
-        <v>2.530145574897095</v>
+        <v>2.60198975641735</v>
       </c>
       <c r="U68">
         <v>0.0503</v>
@@ -7148,7 +7148,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>14.11625167494931</v>
+        <v>13.90556135144261</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7156,22 +7156,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08730639377700575</v>
+        <v>0.08718667872868144</v>
       </c>
       <c r="C69">
-        <v>29.15177414224456</v>
+        <v>27.5767608802678</v>
       </c>
       <c r="D69">
-        <v>-89.33602585775542</v>
+        <v>-89.59443911973219</v>
       </c>
       <c r="E69">
-        <v>82.9522</v>
+        <v>84.2688</v>
       </c>
       <c r="F69">
-        <v>88.21220000000001</v>
+        <v>89.5288</v>
       </c>
       <c r="G69">
         <v>206.7</v>
@@ -7192,28 +7192,28 @@
         <v>61.7</v>
       </c>
       <c r="M69">
-        <v>4.43707366</v>
+        <v>4.50329864</v>
       </c>
       <c r="N69">
-        <v>57.26292634</v>
+        <v>57.19670136000001</v>
       </c>
       <c r="O69">
-        <v>9.448382846100001</v>
+        <v>9.437455724400001</v>
       </c>
       <c r="P69">
-        <v>47.8145434939</v>
+        <v>47.7592456356</v>
       </c>
       <c r="Q69">
-        <v>49.8145434939</v>
+        <v>49.7592456356</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1792910872030478</v>
+        <v>0.1832073085271295</v>
       </c>
       <c r="T69">
-        <v>2.60198975641735</v>
+        <v>2.678324199282621</v>
       </c>
       <c r="U69">
         <v>0.0503</v>
@@ -7230,7 +7230,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>13.90556135144261</v>
+        <v>13.70106780215669</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7238,22 +7238,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08718667872868144</v>
+        <v>0.08706696368035714</v>
       </c>
       <c r="C70">
-        <v>27.5767608802678</v>
+        <v>26.0002483097214</v>
       </c>
       <c r="D70">
-        <v>-89.59443911973219</v>
+        <v>-89.85435169027858</v>
       </c>
       <c r="E70">
-        <v>84.2688</v>
+        <v>85.58540000000001</v>
       </c>
       <c r="F70">
-        <v>89.5288</v>
+        <v>90.84540000000001</v>
       </c>
       <c r="G70">
         <v>206.7</v>
@@ -7274,28 +7274,28 @@
         <v>61.7</v>
       </c>
       <c r="M70">
-        <v>4.50329864</v>
+        <v>4.56952362</v>
       </c>
       <c r="N70">
-        <v>57.19670136000001</v>
+        <v>57.13047638</v>
       </c>
       <c r="O70">
-        <v>9.437455724400001</v>
+        <v>9.426528602700001</v>
       </c>
       <c r="P70">
-        <v>47.7592456356</v>
+        <v>47.7039477773</v>
       </c>
       <c r="Q70">
-        <v>49.7592456356</v>
+        <v>49.7039477773</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1832073085271295</v>
+        <v>0.1873761892914747</v>
       </c>
       <c r="T70">
-        <v>2.678324199282621</v>
+        <v>2.759583444913394</v>
       </c>
       <c r="U70">
         <v>0.0503</v>
@@ -7312,7 +7312,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>13.70106780215669</v>
+        <v>13.50250160212543</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7320,22 +7320,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08706696368035714</v>
+        <v>0.08694724863203282</v>
       </c>
       <c r="C71">
-        <v>26.0002483097214</v>
+        <v>24.42222334420431</v>
       </c>
       <c r="D71">
-        <v>-89.85435169027858</v>
+        <v>-90.11577665579567</v>
       </c>
       <c r="E71">
-        <v>85.58540000000001</v>
+        <v>86.902</v>
       </c>
       <c r="F71">
-        <v>90.84540000000001</v>
+        <v>92.16200000000001</v>
       </c>
       <c r="G71">
         <v>206.7</v>
@@ -7356,28 +7356,28 @@
         <v>61.7</v>
       </c>
       <c r="M71">
-        <v>4.56952362</v>
+        <v>4.6357486</v>
       </c>
       <c r="N71">
-        <v>57.13047638</v>
+        <v>57.0642514</v>
       </c>
       <c r="O71">
-        <v>9.426528602700001</v>
+        <v>9.415601481000001</v>
       </c>
       <c r="P71">
-        <v>47.7039477773</v>
+        <v>47.648649919</v>
       </c>
       <c r="Q71">
-        <v>49.7039477773</v>
+        <v>49.648649919</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1873761892914747</v>
+        <v>0.1918229954401094</v>
       </c>
       <c r="T71">
-        <v>2.759583444913394</v>
+        <v>2.846259973586218</v>
       </c>
       <c r="U71">
         <v>0.0503</v>
@@ -7394,7 +7394,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>13.50250160212543</v>
+        <v>13.30960872209507</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7402,22 +7402,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.08694724863203282</v>
+        <v>0.08682753358370851</v>
       </c>
       <c r="C72">
-        <v>24.42222334420431</v>
+        <v>22.84267274457538</v>
       </c>
       <c r="D72">
-        <v>-90.11577665579567</v>
+        <v>-90.37872725542459</v>
       </c>
       <c r="E72">
-        <v>86.902</v>
+        <v>88.21860000000001</v>
       </c>
       <c r="F72">
-        <v>92.16200000000001</v>
+        <v>93.47860000000001</v>
       </c>
       <c r="G72">
         <v>206.7</v>
@@ -7438,28 +7438,28 @@
         <v>61.7</v>
       </c>
       <c r="M72">
-        <v>4.6357486</v>
+        <v>4.701973580000001</v>
       </c>
       <c r="N72">
-        <v>57.0642514</v>
+        <v>56.99802642</v>
       </c>
       <c r="O72">
-        <v>9.415601481000001</v>
+        <v>9.404674359300001</v>
       </c>
       <c r="P72">
-        <v>47.648649919</v>
+        <v>47.5933520607</v>
       </c>
       <c r="Q72">
-        <v>49.648649919</v>
+        <v>49.5933520607</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1918229954401094</v>
+        <v>0.196576477874857</v>
       </c>
       <c r="T72">
-        <v>2.846259973586218</v>
+        <v>2.938914193891651</v>
       </c>
       <c r="U72">
         <v>0.0503</v>
@@ -7476,7 +7476,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>13.30960872209507</v>
+        <v>13.12214944431908</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7484,22 +7484,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08682753358370851</v>
+        <v>0.0867078185353842</v>
       </c>
       <c r="C73">
-        <v>22.84267274457541</v>
+        <v>21.26158311671823</v>
       </c>
       <c r="D73">
-        <v>-90.37872725542459</v>
+        <v>-90.64321688328177</v>
       </c>
       <c r="E73">
-        <v>88.21859999999998</v>
+        <v>89.53519999999999</v>
       </c>
       <c r="F73">
-        <v>93.47859999999999</v>
+        <v>94.79519999999999</v>
       </c>
       <c r="G73">
         <v>206.7</v>
@@ -7520,28 +7520,28 @@
         <v>61.7</v>
       </c>
       <c r="M73">
-        <v>4.701973579999999</v>
+        <v>4.768198559999999</v>
       </c>
       <c r="N73">
-        <v>56.99802642</v>
+        <v>56.93180144</v>
       </c>
       <c r="O73">
-        <v>9.404674359300001</v>
+        <v>9.393747237600001</v>
       </c>
       <c r="P73">
-        <v>47.5933520607</v>
+        <v>47.5380542024</v>
       </c>
       <c r="Q73">
-        <v>49.5933520607</v>
+        <v>49.5380542024</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1965764778748569</v>
+        <v>0.2016694947692293</v>
       </c>
       <c r="T73">
-        <v>2.938914193891649</v>
+        <v>3.038186572790327</v>
       </c>
       <c r="U73">
         <v>0.0503</v>
@@ -7558,7 +7558,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>13.12214944431908</v>
+        <v>12.93989736870354</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7566,22 +7566,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.0867078185353842</v>
+        <v>0.08750242848705989</v>
       </c>
       <c r="C74">
-        <v>21.26158311671823</v>
+        <v>21.67212479168575</v>
       </c>
       <c r="D74">
-        <v>-90.64321688328177</v>
+        <v>-88.91607520831425</v>
       </c>
       <c r="E74">
-        <v>89.53519999999999</v>
+        <v>90.85179999999998</v>
       </c>
       <c r="F74">
-        <v>94.79519999999999</v>
+        <v>96.11179999999999</v>
       </c>
       <c r="G74">
         <v>206.7</v>
@@ -7602,45 +7602,45 @@
         <v>61.7</v>
       </c>
       <c r="M74">
-        <v>4.768198559999999</v>
+        <v>4.978591239999999</v>
       </c>
       <c r="N74">
-        <v>56.93180144</v>
+        <v>56.72140876</v>
       </c>
       <c r="O74">
-        <v>9.393747237600001</v>
+        <v>9.3590324454</v>
       </c>
       <c r="P74">
-        <v>47.5380542024</v>
+        <v>47.3623763146</v>
       </c>
       <c r="Q74">
-        <v>49.5380542024</v>
+        <v>49.3623763146</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2016694947692293</v>
+        <v>0.2071397721742959</v>
       </c>
       <c r="T74">
-        <v>3.038186572790327</v>
+        <v>3.144812461237054</v>
       </c>
       <c r="U74">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V74">
         <v>0.165</v>
       </c>
       <c r="W74">
-        <v>0.0420005</v>
+        <v>0.043253</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y74">
-        <v>12.93989736870354</v>
+        <v>12.39306402668238</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7648,22 +7648,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08750242848705989</v>
+        <v>0.08739523843873558</v>
       </c>
       <c r="C75">
-        <v>21.67212479168575</v>
+        <v>20.12638994942668</v>
       </c>
       <c r="D75">
-        <v>-88.91607520831425</v>
+        <v>-89.14521005057331</v>
       </c>
       <c r="E75">
-        <v>90.85179999999998</v>
+        <v>92.16839999999999</v>
       </c>
       <c r="F75">
-        <v>96.11179999999999</v>
+        <v>97.4284</v>
       </c>
       <c r="G75">
         <v>206.7</v>
@@ -7684,28 +7684,28 @@
         <v>61.7</v>
       </c>
       <c r="M75">
-        <v>4.978591239999999</v>
+        <v>5.04679112</v>
       </c>
       <c r="N75">
-        <v>56.72140876</v>
+        <v>56.65320888</v>
       </c>
       <c r="O75">
-        <v>9.3590324454</v>
+        <v>9.3477794652</v>
       </c>
       <c r="P75">
-        <v>47.3623763146</v>
+        <v>47.3054294148</v>
       </c>
       <c r="Q75">
-        <v>49.3623763146</v>
+        <v>49.3054294148</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2071397721742959</v>
+        <v>0.213030840148983</v>
       </c>
       <c r="T75">
-        <v>3.144812461237054</v>
+        <v>3.259640341102761</v>
       </c>
       <c r="U75">
         <v>0.0518</v>
@@ -7722,7 +7722,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>12.39306402668238</v>
+        <v>12.22559018848396</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7730,22 +7730,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08739523843873558</v>
+        <v>0.08728804839041127</v>
       </c>
       <c r="C76">
-        <v>20.12638994942668</v>
+        <v>18.57947110474922</v>
       </c>
       <c r="D76">
-        <v>-89.14521005057331</v>
+        <v>-89.37552889525077</v>
       </c>
       <c r="E76">
-        <v>92.16839999999999</v>
+        <v>93.485</v>
       </c>
       <c r="F76">
-        <v>97.4284</v>
+        <v>98.745</v>
       </c>
       <c r="G76">
         <v>206.7</v>
@@ -7766,28 +7766,28 @@
         <v>61.7</v>
       </c>
       <c r="M76">
-        <v>5.04679112</v>
+        <v>5.114991</v>
       </c>
       <c r="N76">
-        <v>56.65320888</v>
+        <v>56.585009</v>
       </c>
       <c r="O76">
-        <v>9.3477794652</v>
+        <v>9.336526485</v>
       </c>
       <c r="P76">
-        <v>47.3054294148</v>
+        <v>47.248482515</v>
       </c>
       <c r="Q76">
-        <v>49.3054294148</v>
+        <v>49.248482515</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.213030840148983</v>
+        <v>0.219393193561645</v>
       </c>
       <c r="T76">
-        <v>3.259640341102761</v>
+        <v>3.383654451357724</v>
       </c>
       <c r="U76">
         <v>0.0518</v>
@@ -7804,7 +7804,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>12.22559018848396</v>
+        <v>12.06258231930418</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7812,22 +7812,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08728804839041127</v>
+        <v>0.08718085834208694</v>
       </c>
       <c r="C77">
-        <v>18.57947110474922</v>
+        <v>17.03135905678501</v>
       </c>
       <c r="D77">
-        <v>-89.37552889525077</v>
+        <v>-89.60704094321498</v>
       </c>
       <c r="E77">
-        <v>93.485</v>
+        <v>94.80159999999999</v>
       </c>
       <c r="F77">
-        <v>98.745</v>
+        <v>100.0616</v>
       </c>
       <c r="G77">
         <v>206.7</v>
@@ -7848,28 +7848,28 @@
         <v>61.7</v>
       </c>
       <c r="M77">
-        <v>5.114991</v>
+        <v>5.18319088</v>
       </c>
       <c r="N77">
-        <v>56.585009</v>
+        <v>56.51680912</v>
       </c>
       <c r="O77">
-        <v>9.336526485</v>
+        <v>9.325273504800002</v>
       </c>
       <c r="P77">
-        <v>47.248482515</v>
+        <v>47.1915356152</v>
       </c>
       <c r="Q77">
-        <v>49.248482515</v>
+        <v>49.1915356152</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.219393193561645</v>
+        <v>0.226285743092029</v>
       </c>
       <c r="T77">
-        <v>3.383654451357724</v>
+        <v>3.518003070800602</v>
       </c>
       <c r="U77">
         <v>0.0518</v>
@@ -7886,7 +7886,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>12.06258231930418</v>
+        <v>11.90386413089228</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7894,22 +7894,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08718085834208694</v>
+        <v>0.08707366829376263</v>
       </c>
       <c r="C78">
-        <v>17.03135905678501</v>
+        <v>15.48204450908503</v>
       </c>
       <c r="D78">
-        <v>-89.60704094321498</v>
+        <v>-89.83975549091495</v>
       </c>
       <c r="E78">
-        <v>94.80159999999999</v>
+        <v>96.1182</v>
       </c>
       <c r="F78">
-        <v>100.0616</v>
+        <v>101.3782</v>
       </c>
       <c r="G78">
         <v>206.7</v>
@@ -7930,28 +7930,28 @@
         <v>61.7</v>
       </c>
       <c r="M78">
-        <v>5.18319088</v>
+        <v>5.25139076</v>
       </c>
       <c r="N78">
-        <v>56.51680912</v>
+        <v>56.44860924</v>
       </c>
       <c r="O78">
-        <v>9.325273504800002</v>
+        <v>9.314020524600002</v>
       </c>
       <c r="P78">
-        <v>47.1915356152</v>
+        <v>47.1345887154</v>
       </c>
       <c r="Q78">
-        <v>49.1915356152</v>
+        <v>49.1345887154</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.226285743092029</v>
+        <v>0.2337776447554897</v>
       </c>
       <c r="T78">
-        <v>3.518003070800602</v>
+        <v>3.664034178890685</v>
       </c>
       <c r="U78">
         <v>0.0518</v>
@@ -7968,7 +7968,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>11.90386413089228</v>
+        <v>11.74926849282875</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7976,22 +7976,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08707366829376263</v>
+        <v>0.08696647824543832</v>
       </c>
       <c r="C79">
-        <v>15.48204450908503</v>
+        <v>13.93151806837517</v>
       </c>
       <c r="D79">
-        <v>-89.83975549091495</v>
+        <v>-90.07368193162482</v>
       </c>
       <c r="E79">
-        <v>96.1182</v>
+        <v>97.4348</v>
       </c>
       <c r="F79">
-        <v>101.3782</v>
+        <v>102.6948</v>
       </c>
       <c r="G79">
         <v>206.7</v>
@@ -8012,28 +8012,28 @@
         <v>61.7</v>
       </c>
       <c r="M79">
-        <v>5.25139076</v>
+        <v>5.319590639999999</v>
       </c>
       <c r="N79">
-        <v>56.44860924</v>
+        <v>56.38040936</v>
       </c>
       <c r="O79">
-        <v>9.314020524600002</v>
+        <v>9.3027675444</v>
       </c>
       <c r="P79">
-        <v>47.1345887154</v>
+        <v>47.0776418156</v>
       </c>
       <c r="Q79">
-        <v>49.1345887154</v>
+        <v>49.0776418156</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2337776447554897</v>
+        <v>0.241950628388356</v>
       </c>
       <c r="T79">
-        <v>3.664034178890685</v>
+        <v>3.823340842261685</v>
       </c>
       <c r="U79">
         <v>0.0518</v>
@@ -8050,7 +8050,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>11.74926849282875</v>
+        <v>11.59863684548479</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8058,22 +8058,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08696647824543832</v>
+        <v>0.086859288197114</v>
       </c>
       <c r="C80">
-        <v>13.93151806837517</v>
+        <v>12.37977024329233</v>
       </c>
       <c r="D80">
-        <v>-90.07368193162482</v>
+        <v>-90.30882975670765</v>
       </c>
       <c r="E80">
-        <v>97.4348</v>
+        <v>98.7514</v>
       </c>
       <c r="F80">
-        <v>102.6948</v>
+        <v>104.0114</v>
       </c>
       <c r="G80">
         <v>206.7</v>
@@ -8094,28 +8094,28 @@
         <v>61.7</v>
       </c>
       <c r="M80">
-        <v>5.319590639999999</v>
+        <v>5.38779052</v>
       </c>
       <c r="N80">
-        <v>56.38040936</v>
+        <v>56.31220948</v>
       </c>
       <c r="O80">
-        <v>9.3027675444</v>
+        <v>9.2915145642</v>
       </c>
       <c r="P80">
-        <v>47.0776418156</v>
+        <v>47.0206949158</v>
       </c>
       <c r="Q80">
-        <v>49.0776418156</v>
+        <v>49.0206949158</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.241950628388356</v>
+        <v>0.2509019914148287</v>
       </c>
       <c r="T80">
-        <v>3.823340842261685</v>
+        <v>3.997819568810877</v>
       </c>
       <c r="U80">
         <v>0.0518</v>
@@ -8132,7 +8132,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>11.59863684548479</v>
+        <v>11.45181865756726</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8140,22 +8140,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.086859288197114</v>
+        <v>0.08675209814878969</v>
       </c>
       <c r="C81">
-        <v>12.37977024329233</v>
+        <v>10.82679144310087</v>
       </c>
       <c r="D81">
-        <v>-90.30882975670765</v>
+        <v>-90.54520855689911</v>
       </c>
       <c r="E81">
-        <v>98.7514</v>
+        <v>100.068</v>
       </c>
       <c r="F81">
-        <v>104.0114</v>
+        <v>105.328</v>
       </c>
       <c r="G81">
         <v>206.7</v>
@@ -8176,28 +8176,28 @@
         <v>61.7</v>
       </c>
       <c r="M81">
-        <v>5.38779052</v>
+        <v>5.4559904</v>
       </c>
       <c r="N81">
-        <v>56.31220948</v>
+        <v>56.24400960000001</v>
       </c>
       <c r="O81">
-        <v>9.2915145642</v>
+        <v>9.280261584000002</v>
       </c>
       <c r="P81">
-        <v>47.0206949158</v>
+        <v>46.963748016</v>
       </c>
       <c r="Q81">
-        <v>49.0206949158</v>
+        <v>48.963748016</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2509019914148287</v>
+        <v>0.2607484907439485</v>
       </c>
       <c r="T81">
-        <v>3.997819568810877</v>
+        <v>4.189746168014986</v>
       </c>
       <c r="U81">
         <v>0.0518</v>
@@ -8214,7 +8214,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>11.45181865756726</v>
+        <v>11.30867092434767</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8222,22 +8222,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08675209814878969</v>
+        <v>0.08664490810046538</v>
       </c>
       <c r="C82">
-        <v>10.82679144310087</v>
+        <v>9.272571976388491</v>
       </c>
       <c r="D82">
-        <v>-90.54520855689911</v>
+        <v>-90.78282802361149</v>
       </c>
       <c r="E82">
-        <v>100.068</v>
+        <v>101.3846</v>
       </c>
       <c r="F82">
-        <v>105.328</v>
+        <v>106.6446</v>
       </c>
       <c r="G82">
         <v>206.7</v>
@@ -8258,28 +8258,28 @@
         <v>61.7</v>
       </c>
       <c r="M82">
-        <v>5.4559904</v>
+        <v>5.524190280000001</v>
       </c>
       <c r="N82">
-        <v>56.24400960000001</v>
+        <v>56.17580972</v>
       </c>
       <c r="O82">
-        <v>9.280261584000002</v>
+        <v>9.269008603800001</v>
       </c>
       <c r="P82">
-        <v>46.963748016</v>
+        <v>46.9068011162</v>
       </c>
       <c r="Q82">
-        <v>48.963748016</v>
+        <v>48.9068011162</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2607484907439485</v>
+        <v>0.27163146368666</v>
       </c>
       <c r="T82">
-        <v>4.189746168014986</v>
+        <v>4.401875567135319</v>
       </c>
       <c r="U82">
         <v>0.0518</v>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>11.30867092434767</v>
+        <v>11.16905770305942</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8304,22 +8304,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08664490810046538</v>
+        <v>0.08653771805214105</v>
       </c>
       <c r="C83">
-        <v>9.272571976388491</v>
+        <v>7.717102049741783</v>
       </c>
       <c r="D83">
-        <v>-90.78282802361149</v>
+        <v>-91.0216979502582</v>
       </c>
       <c r="E83">
-        <v>101.3846</v>
+        <v>102.7012</v>
       </c>
       <c r="F83">
-        <v>106.6446</v>
+        <v>107.9612</v>
       </c>
       <c r="G83">
         <v>206.7</v>
@@ -8340,28 +8340,28 @@
         <v>61.7</v>
       </c>
       <c r="M83">
-        <v>5.524190280000001</v>
+        <v>5.59239016</v>
       </c>
       <c r="N83">
-        <v>56.17580972</v>
+        <v>56.10760984</v>
       </c>
       <c r="O83">
-        <v>9.269008603800001</v>
+        <v>9.257755623600001</v>
       </c>
       <c r="P83">
-        <v>46.9068011162</v>
+        <v>46.8498542164</v>
       </c>
       <c r="Q83">
-        <v>48.9068011162</v>
+        <v>48.8498542164</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.27163146368666</v>
+        <v>0.2837236558452282</v>
       </c>
       <c r="T83">
-        <v>4.401875567135319</v>
+        <v>4.637574899491243</v>
       </c>
       <c r="U83">
         <v>0.0518</v>
@@ -8378,7 +8378,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>11.16905770305942</v>
+        <v>11.03284968229041</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8386,22 +8386,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08653771805214105</v>
+        <v>0.08643052800381675</v>
       </c>
       <c r="C84">
-        <v>7.717102049741783</v>
+        <v>6.160371766400829</v>
       </c>
       <c r="D84">
-        <v>-91.0216979502582</v>
+        <v>-91.26182823359915</v>
       </c>
       <c r="E84">
-        <v>102.7012</v>
+        <v>104.0178</v>
       </c>
       <c r="F84">
-        <v>107.9612</v>
+        <v>109.2778</v>
       </c>
       <c r="G84">
         <v>206.7</v>
@@ -8422,28 +8422,28 @@
         <v>61.7</v>
       </c>
       <c r="M84">
-        <v>5.59239016</v>
+        <v>5.660590040000001</v>
       </c>
       <c r="N84">
-        <v>56.10760984</v>
+        <v>56.03940996</v>
       </c>
       <c r="O84">
-        <v>9.257755623600001</v>
+        <v>9.246502643400001</v>
       </c>
       <c r="P84">
-        <v>46.8498542164</v>
+        <v>46.7929073166</v>
       </c>
       <c r="Q84">
-        <v>48.8498542164</v>
+        <v>48.7929073166</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2837236558452282</v>
+        <v>0.297238458845981</v>
       </c>
       <c r="T84">
-        <v>4.637574899491243</v>
+        <v>4.901003565065511</v>
       </c>
       <c r="U84">
         <v>0.0518</v>
@@ -8460,7 +8460,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>11.03284968229041</v>
+        <v>10.89992378250377</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8468,22 +8468,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08643052800381675</v>
+        <v>0.08632333795549245</v>
       </c>
       <c r="C85">
-        <v>6.160371766400829</v>
+        <v>4.602371124892287</v>
       </c>
       <c r="D85">
-        <v>-91.26182823359915</v>
+        <v>-91.50322887510769</v>
       </c>
       <c r="E85">
-        <v>104.0178</v>
+        <v>105.3344</v>
       </c>
       <c r="F85">
-        <v>109.2778</v>
+        <v>110.5944</v>
       </c>
       <c r="G85">
         <v>206.7</v>
@@ -8504,28 +8504,28 @@
         <v>61.7</v>
       </c>
       <c r="M85">
-        <v>5.660590040000001</v>
+        <v>5.728789920000001</v>
       </c>
       <c r="N85">
-        <v>56.03940996</v>
+        <v>55.97121008000001</v>
       </c>
       <c r="O85">
-        <v>9.246502643400001</v>
+        <v>9.235249663200001</v>
       </c>
       <c r="P85">
-        <v>46.7929073166</v>
+        <v>46.7359604168</v>
       </c>
       <c r="Q85">
-        <v>48.7929073166</v>
+        <v>48.7359604168</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.297238458845981</v>
+        <v>0.312442612221828</v>
       </c>
       <c r="T85">
-        <v>4.901003565065511</v>
+        <v>5.197360813836565</v>
       </c>
       <c r="U85">
         <v>0.0518</v>
@@ -8542,7 +8542,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>10.89992378250377</v>
+        <v>10.77016278509302</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8550,22 +8550,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08632333795549246</v>
+        <v>0.08621614790716814</v>
       </c>
       <c r="C86">
-        <v>4.602371124892329</v>
+        <v>3.043090017640779</v>
       </c>
       <c r="D86">
-        <v>-91.50322887510767</v>
+        <v>-91.74590998235922</v>
       </c>
       <c r="E86">
-        <v>105.3344</v>
+        <v>106.651</v>
       </c>
       <c r="F86">
-        <v>110.5944</v>
+        <v>111.911</v>
       </c>
       <c r="G86">
         <v>206.7</v>
@@ -8586,28 +8586,28 @@
         <v>61.7</v>
       </c>
       <c r="M86">
-        <v>5.72878992</v>
+        <v>5.7969898</v>
       </c>
       <c r="N86">
-        <v>55.97121008000001</v>
+        <v>55.9030102</v>
       </c>
       <c r="O86">
-        <v>9.235249663200001</v>
+        <v>9.223996683000001</v>
       </c>
       <c r="P86">
-        <v>46.7359604168</v>
+        <v>46.679013517</v>
       </c>
       <c r="Q86">
-        <v>48.7359604168</v>
+        <v>48.679013517</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3124426122218278</v>
+        <v>0.3296739860477875</v>
       </c>
       <c r="T86">
-        <v>5.197360813836561</v>
+        <v>5.533232362443753</v>
       </c>
       <c r="U86">
         <v>0.0518</v>
@@ -8624,7 +8624,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>10.77016278509302</v>
+        <v>10.64345498762134</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8632,22 +8632,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08621614790716814</v>
+        <v>0.08610895785884382</v>
       </c>
       <c r="C87">
-        <v>3.043090017640779</v>
+        <v>1.482518229558195</v>
       </c>
       <c r="D87">
-        <v>-91.74590998235922</v>
+        <v>-91.9898817704418</v>
       </c>
       <c r="E87">
-        <v>106.651</v>
+        <v>107.9676</v>
       </c>
       <c r="F87">
-        <v>111.911</v>
+        <v>113.2276</v>
       </c>
       <c r="G87">
         <v>206.7</v>
@@ -8668,28 +8668,28 @@
         <v>61.7</v>
       </c>
       <c r="M87">
-        <v>5.7969898</v>
+        <v>5.865189679999999</v>
       </c>
       <c r="N87">
-        <v>55.9030102</v>
+        <v>55.83481032</v>
       </c>
       <c r="O87">
-        <v>9.223996683000001</v>
+        <v>9.212743702800001</v>
       </c>
       <c r="P87">
-        <v>46.679013517</v>
+        <v>46.62206661720001</v>
       </c>
       <c r="Q87">
-        <v>48.679013517</v>
+        <v>48.62206661720001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3296739860477875</v>
+        <v>0.3493669847060273</v>
       </c>
       <c r="T87">
-        <v>5.533232362443753</v>
+        <v>5.917085560851973</v>
       </c>
       <c r="U87">
         <v>0.0518</v>
@@ -8706,7 +8706,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>10.64345498762134</v>
+        <v>10.51969388311411</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8714,22 +8714,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08610895785884382</v>
+        <v>0.08600176781051952</v>
       </c>
       <c r="C88">
-        <v>1.482518229558195</v>
+        <v>-0.07935456338948654</v>
       </c>
       <c r="D88">
-        <v>-91.9898817704418</v>
+        <v>-92.23515456338949</v>
       </c>
       <c r="E88">
-        <v>107.9676</v>
+        <v>109.2842</v>
       </c>
       <c r="F88">
-        <v>113.2276</v>
+        <v>114.5442</v>
       </c>
       <c r="G88">
         <v>206.7</v>
@@ -8750,28 +8750,28 @@
         <v>61.7</v>
       </c>
       <c r="M88">
-        <v>5.865189679999999</v>
+        <v>5.933389559999999</v>
       </c>
       <c r="N88">
-        <v>55.83481032</v>
+        <v>55.76661044</v>
       </c>
       <c r="O88">
-        <v>9.212743702800001</v>
+        <v>9.201490722600001</v>
       </c>
       <c r="P88">
-        <v>46.62206661720001</v>
+        <v>46.5651197174</v>
       </c>
       <c r="Q88">
-        <v>48.62206661720001</v>
+        <v>48.5651197174</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3493669847060273</v>
+        <v>0.3720896754655347</v>
       </c>
       <c r="T88">
-        <v>5.917085560851973</v>
+        <v>6.359993097476842</v>
       </c>
       <c r="U88">
         <v>0.0518</v>
@@ -8788,7 +8788,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>10.51969388311411</v>
+        <v>10.39877786146912</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8796,22 +8796,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08600176781051952</v>
+        <v>0.0858945777621952</v>
       </c>
       <c r="C89">
-        <v>-0.07935456338948654</v>
+        <v>-1.642538795638799</v>
       </c>
       <c r="D89">
-        <v>-92.23515456338949</v>
+        <v>-92.48173879563879</v>
       </c>
       <c r="E89">
-        <v>109.2842</v>
+        <v>110.6008</v>
       </c>
       <c r="F89">
-        <v>114.5442</v>
+        <v>115.8608</v>
       </c>
       <c r="G89">
         <v>206.7</v>
@@ -8832,28 +8832,28 @@
         <v>61.7</v>
       </c>
       <c r="M89">
-        <v>5.933389559999999</v>
+        <v>6.00158944</v>
       </c>
       <c r="N89">
-        <v>55.76661044</v>
+        <v>55.69841056</v>
       </c>
       <c r="O89">
-        <v>9.201490722600001</v>
+        <v>9.190237742400001</v>
       </c>
       <c r="P89">
-        <v>46.5651197174</v>
+        <v>46.5081728176</v>
       </c>
       <c r="Q89">
-        <v>48.5651197174</v>
+        <v>48.5081728176</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3720896754655347</v>
+        <v>0.3985994813516267</v>
       </c>
       <c r="T89">
-        <v>6.359993097476842</v>
+        <v>6.876718556872524</v>
       </c>
       <c r="U89">
         <v>0.0518</v>
@@ -8870,7 +8870,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>10.39877786146912</v>
+        <v>10.28060993122515</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8878,22 +8878,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.0858945777621952</v>
+        <v>0.08578738771387087</v>
       </c>
       <c r="C90">
-        <v>-1.642538795638799</v>
+        <v>-3.207045013508193</v>
       </c>
       <c r="D90">
-        <v>-92.48173879563879</v>
+        <v>-92.72964501350818</v>
       </c>
       <c r="E90">
-        <v>110.6008</v>
+        <v>111.9174</v>
       </c>
       <c r="F90">
-        <v>115.8608</v>
+        <v>117.1774</v>
       </c>
       <c r="G90">
         <v>206.7</v>
@@ -8914,28 +8914,28 @@
         <v>61.7</v>
       </c>
       <c r="M90">
-        <v>6.00158944</v>
+        <v>6.06978932</v>
       </c>
       <c r="N90">
-        <v>55.69841056</v>
+        <v>55.63021068</v>
       </c>
       <c r="O90">
-        <v>9.190237742400001</v>
+        <v>9.178984762200001</v>
       </c>
       <c r="P90">
-        <v>46.5081728176</v>
+        <v>46.4512259178</v>
       </c>
       <c r="Q90">
-        <v>48.5081728176</v>
+        <v>48.4512259178</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3985994813516267</v>
+        <v>0.4299292519442808</v>
       </c>
       <c r="T90">
-        <v>6.876718556872524</v>
+        <v>7.48739409979469</v>
       </c>
       <c r="U90">
         <v>0.0518</v>
@@ -8952,7 +8952,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>10.28060993122515</v>
+        <v>10.16509746008779</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8960,22 +8960,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08578738771387087</v>
+        <v>0.08568019766554658</v>
       </c>
       <c r="C91">
-        <v>-3.207045013508193</v>
+        <v>-4.772883876701684</v>
       </c>
       <c r="D91">
-        <v>-92.72964501350818</v>
+        <v>-92.97888387670167</v>
       </c>
       <c r="E91">
-        <v>111.9174</v>
+        <v>113.234</v>
       </c>
       <c r="F91">
-        <v>117.1774</v>
+        <v>118.494</v>
       </c>
       <c r="G91">
         <v>206.7</v>
@@ -8996,28 +8996,28 @@
         <v>61.7</v>
       </c>
       <c r="M91">
-        <v>6.06978932</v>
+        <v>6.1379892</v>
       </c>
       <c r="N91">
-        <v>55.63021068</v>
+        <v>55.5620108</v>
       </c>
       <c r="O91">
-        <v>9.178984762200001</v>
+        <v>9.167731782000001</v>
       </c>
       <c r="P91">
-        <v>46.4512259178</v>
+        <v>46.39427901800001</v>
       </c>
       <c r="Q91">
-        <v>48.4512259178</v>
+        <v>48.39427901800001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4299292519442808</v>
+        <v>0.4675249766554658</v>
       </c>
       <c r="T91">
-        <v>7.48739409979469</v>
+        <v>8.220204751301292</v>
       </c>
       <c r="U91">
         <v>0.0518</v>
@@ -9034,7 +9034,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>10.16509746008779</v>
+        <v>10.05215193275348</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9042,22 +9042,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.08568019766554658</v>
+        <v>0.08557300761722225</v>
       </c>
       <c r="C92">
-        <v>-4.772883876701684</v>
+        <v>-6.340066159837093</v>
       </c>
       <c r="D92">
-        <v>-92.97888387670167</v>
+        <v>-93.22946615983707</v>
       </c>
       <c r="E92">
-        <v>113.234</v>
+        <v>114.5506</v>
       </c>
       <c r="F92">
-        <v>118.494</v>
+        <v>119.8106</v>
       </c>
       <c r="G92">
         <v>206.7</v>
@@ -9078,28 +9078,28 @@
         <v>61.7</v>
       </c>
       <c r="M92">
-        <v>6.1379892</v>
+        <v>6.206189080000001</v>
       </c>
       <c r="N92">
-        <v>55.5620108</v>
+        <v>55.49381092</v>
       </c>
       <c r="O92">
-        <v>9.167731782000001</v>
+        <v>9.156478801800001</v>
       </c>
       <c r="P92">
-        <v>46.39427901800001</v>
+        <v>46.3373321182</v>
       </c>
       <c r="Q92">
-        <v>48.39427901800001</v>
+        <v>48.3373321182</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4675249766554658</v>
+        <v>0.5134753068580252</v>
       </c>
       <c r="T92">
-        <v>8.220204751301292</v>
+        <v>9.115862214253806</v>
       </c>
       <c r="U92">
         <v>0.0518</v>
@@ -9116,7 +9116,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>10.05215193275348</v>
+        <v>9.941688724701246</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9124,22 +9124,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.08557300761722225</v>
+        <v>0.08546581756889796</v>
       </c>
       <c r="C93">
-        <v>-6.340066159837093</v>
+        <v>-7.908602753998125</v>
       </c>
       <c r="D93">
-        <v>-93.22946615983707</v>
+        <v>-93.48140275399811</v>
       </c>
       <c r="E93">
-        <v>114.5506</v>
+        <v>115.8672</v>
       </c>
       <c r="F93">
-        <v>119.8106</v>
+        <v>121.1272</v>
       </c>
       <c r="G93">
         <v>206.7</v>
@@ -9160,28 +9160,28 @@
         <v>61.7</v>
       </c>
       <c r="M93">
-        <v>6.206189080000001</v>
+        <v>6.27438896</v>
       </c>
       <c r="N93">
-        <v>55.49381092</v>
+        <v>55.42561104000001</v>
       </c>
       <c r="O93">
-        <v>9.156478801800001</v>
+        <v>9.145225821600002</v>
       </c>
       <c r="P93">
-        <v>46.3373321182</v>
+        <v>46.28038521840001</v>
       </c>
       <c r="Q93">
-        <v>48.3373321182</v>
+        <v>48.28038521840001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5134753068580252</v>
+        <v>0.5709132196112247</v>
       </c>
       <c r="T93">
-        <v>9.115862214253806</v>
+        <v>10.23543404294445</v>
       </c>
       <c r="U93">
         <v>0.0518</v>
@@ -9198,7 +9198,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>9.941688724701246</v>
+        <v>9.833626890737104</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9206,22 +9206,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.08546581756889796</v>
+        <v>0.08667876252057363</v>
       </c>
       <c r="C94">
-        <v>-7.908602753998125</v>
+        <v>-6.451444730159807</v>
       </c>
       <c r="D94">
-        <v>-93.48140275399811</v>
+        <v>-90.70764473015979</v>
       </c>
       <c r="E94">
-        <v>115.8672</v>
+        <v>117.1838</v>
       </c>
       <c r="F94">
-        <v>121.1272</v>
+        <v>122.4438</v>
       </c>
       <c r="G94">
         <v>206.7</v>
@@ -9242,45 +9242,45 @@
         <v>61.7</v>
       </c>
       <c r="M94">
-        <v>6.27438896</v>
+        <v>6.550743300000001</v>
       </c>
       <c r="N94">
-        <v>55.42561104000001</v>
+        <v>55.1492567</v>
       </c>
       <c r="O94">
-        <v>9.145225821600002</v>
+        <v>9.099627355500001</v>
       </c>
       <c r="P94">
-        <v>46.28038521840001</v>
+        <v>46.0496293445</v>
       </c>
       <c r="Q94">
-        <v>48.28038521840001</v>
+        <v>48.0496293445</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5709132196112247</v>
+        <v>0.6447619645796238</v>
       </c>
       <c r="T94">
-        <v>10.23543404294445</v>
+        <v>11.67488353697527</v>
       </c>
       <c r="U94">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V94">
         <v>0.165</v>
       </c>
       <c r="W94">
-        <v>0.043253</v>
+        <v>0.0446725</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y94">
-        <v>9.833626890737104</v>
+        <v>9.418778476634857</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9288,22 +9288,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.08667876252057363</v>
+        <v>0.08658576747224932</v>
       </c>
       <c r="C95">
-        <v>-6.451444730159807</v>
+        <v>-7.974865940789343</v>
       </c>
       <c r="D95">
-        <v>-90.70764473015979</v>
+        <v>-90.91446594078933</v>
       </c>
       <c r="E95">
-        <v>117.1838</v>
+        <v>118.5004</v>
       </c>
       <c r="F95">
-        <v>122.4438</v>
+        <v>123.7604</v>
       </c>
       <c r="G95">
         <v>206.7</v>
@@ -9324,28 +9324,28 @@
         <v>61.7</v>
       </c>
       <c r="M95">
-        <v>6.550743300000001</v>
+        <v>6.6211814</v>
       </c>
       <c r="N95">
-        <v>55.1492567</v>
+        <v>55.07881860000001</v>
       </c>
       <c r="O95">
-        <v>9.099627355500001</v>
+        <v>9.088005069000001</v>
       </c>
       <c r="P95">
-        <v>46.0496293445</v>
+        <v>45.990813531</v>
       </c>
       <c r="Q95">
-        <v>48.0496293445</v>
+        <v>47.990813531</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6447619645796238</v>
+        <v>0.7432269578708227</v>
       </c>
       <c r="T95">
-        <v>11.67488353697527</v>
+        <v>13.59414952901638</v>
       </c>
       <c r="U95">
         <v>0.0535</v>
@@ -9362,7 +9362,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>9.418778476634857</v>
+        <v>9.318578705606829</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9370,22 +9370,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08658576747224932</v>
+        <v>0.08649277242392502</v>
       </c>
       <c r="C96">
-        <v>-7.974865940789343</v>
+        <v>-9.499232446975384</v>
       </c>
       <c r="D96">
-        <v>-90.91446594078933</v>
+        <v>-91.12223244697536</v>
       </c>
       <c r="E96">
-        <v>118.5004</v>
+        <v>119.817</v>
       </c>
       <c r="F96">
-        <v>123.7604</v>
+        <v>125.077</v>
       </c>
       <c r="G96">
         <v>206.7</v>
@@ -9406,28 +9406,28 @@
         <v>61.7</v>
       </c>
       <c r="M96">
-        <v>6.6211814</v>
+        <v>6.691619500000001</v>
       </c>
       <c r="N96">
-        <v>55.07881860000001</v>
+        <v>55.0083805</v>
       </c>
       <c r="O96">
-        <v>9.088005069000001</v>
+        <v>9.076382782500001</v>
       </c>
       <c r="P96">
-        <v>45.990813531</v>
+        <v>45.9319977175</v>
       </c>
       <c r="Q96">
-        <v>47.990813531</v>
+        <v>47.9319977175</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7432269578708227</v>
+        <v>0.8810779484785014</v>
       </c>
       <c r="T96">
-        <v>13.59414952901638</v>
+        <v>16.28112191787393</v>
       </c>
       <c r="U96">
         <v>0.0535</v>
@@ -9444,7 +9444,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>9.318578705606829</v>
+        <v>9.220488403442545</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9452,22 +9452,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.08649277242392502</v>
+        <v>0.0863997773756007</v>
       </c>
       <c r="C97">
-        <v>-9.499232446975384</v>
+        <v>-11.02455074440422</v>
       </c>
       <c r="D97">
-        <v>-91.12223244697536</v>
+        <v>-91.33095074440421</v>
       </c>
       <c r="E97">
-        <v>119.817</v>
+        <v>121.1336</v>
       </c>
       <c r="F97">
-        <v>125.077</v>
+        <v>126.3936</v>
       </c>
       <c r="G97">
         <v>206.7</v>
@@ -9488,28 +9488,28 @@
         <v>61.7</v>
       </c>
       <c r="M97">
-        <v>6.691619500000001</v>
+        <v>6.7620576</v>
       </c>
       <c r="N97">
-        <v>55.0083805</v>
+        <v>54.9379424</v>
       </c>
       <c r="O97">
-        <v>9.076382782500001</v>
+        <v>9.064760496000002</v>
       </c>
       <c r="P97">
-        <v>45.9319977175</v>
+        <v>45.87318190400001</v>
       </c>
       <c r="Q97">
-        <v>47.9319977175</v>
+        <v>47.87318190400001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8810779484785014</v>
+        <v>1.087854434390019</v>
       </c>
       <c r="T97">
-        <v>16.28112191787393</v>
+        <v>20.31158050116024</v>
       </c>
       <c r="U97">
         <v>0.0535</v>
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>9.220488403442545</v>
+        <v>9.124441649240019</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9534,22 +9534,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.0863997773756007</v>
+        <v>0.0863067823272764</v>
       </c>
       <c r="C98">
-        <v>-11.02455074440421</v>
+        <v>-12.55082738841305</v>
       </c>
       <c r="D98">
-        <v>-91.33095074440421</v>
+        <v>-91.54062738841306</v>
       </c>
       <c r="E98">
-        <v>121.1336</v>
+        <v>122.4502</v>
       </c>
       <c r="F98">
-        <v>126.3936</v>
+        <v>127.7102</v>
       </c>
       <c r="G98">
         <v>206.7</v>
@@ -9570,28 +9570,28 @@
         <v>61.7</v>
       </c>
       <c r="M98">
-        <v>6.762057599999999</v>
+        <v>6.832495699999999</v>
       </c>
       <c r="N98">
-        <v>54.9379424</v>
+        <v>54.86750430000001</v>
       </c>
       <c r="O98">
-        <v>9.064760496000002</v>
+        <v>9.053138209500002</v>
       </c>
       <c r="P98">
-        <v>45.87318190400001</v>
+        <v>45.8143660905</v>
       </c>
       <c r="Q98">
-        <v>47.87318190400001</v>
+        <v>47.8143660905</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.087854434390017</v>
+        <v>1.432481910909212</v>
       </c>
       <c r="T98">
-        <v>20.31158050116019</v>
+        <v>27.02901147330403</v>
       </c>
       <c r="U98">
         <v>0.0535</v>
@@ -9608,7 +9608,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>9.124441649240019</v>
+        <v>9.030375240484968</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9616,22 +9616,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.0863067823272764</v>
+        <v>0.08621378727895207</v>
       </c>
       <c r="C99">
-        <v>-12.55082738841305</v>
+        <v>-14.07806899467643</v>
       </c>
       <c r="D99">
-        <v>-91.54062738841306</v>
+        <v>-91.75126899467644</v>
       </c>
       <c r="E99">
-        <v>122.4502</v>
+        <v>123.7668</v>
       </c>
       <c r="F99">
-        <v>127.7102</v>
+        <v>129.0268</v>
       </c>
       <c r="G99">
         <v>206.7</v>
@@ -9652,28 +9652,28 @@
         <v>61.7</v>
       </c>
       <c r="M99">
-        <v>6.832495699999999</v>
+        <v>6.902933799999999</v>
       </c>
       <c r="N99">
-        <v>54.86750430000001</v>
+        <v>54.7970662</v>
       </c>
       <c r="O99">
-        <v>9.053138209500002</v>
+        <v>9.041515923</v>
       </c>
       <c r="P99">
-        <v>45.8143660905</v>
+        <v>45.755550277</v>
       </c>
       <c r="Q99">
-        <v>47.8143660905</v>
+        <v>47.755550277</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.432481910909212</v>
+        <v>2.121736863947602</v>
       </c>
       <c r="T99">
-        <v>27.02901147330403</v>
+        <v>40.4638734175917</v>
       </c>
       <c r="U99">
         <v>0.0535</v>
@@ -9690,7 +9690,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>9.030375240484968</v>
+        <v>8.938228554357572</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9698,22 +9698,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.08621378727895207</v>
+        <v>0.08612079223062775</v>
       </c>
       <c r="C100">
-        <v>-14.07806899467643</v>
+        <v>-15.60628223990173</v>
       </c>
       <c r="D100">
-        <v>-91.75126899467644</v>
+        <v>-91.96288223990172</v>
       </c>
       <c r="E100">
-        <v>123.7668</v>
+        <v>125.0834</v>
       </c>
       <c r="F100">
-        <v>129.0268</v>
+        <v>130.3434</v>
       </c>
       <c r="G100">
         <v>206.7</v>
@@ -9734,28 +9734,28 @@
         <v>61.7</v>
       </c>
       <c r="M100">
-        <v>6.902933799999999</v>
+        <v>6.9733719</v>
       </c>
       <c r="N100">
-        <v>54.7970662</v>
+        <v>54.7266281</v>
       </c>
       <c r="O100">
-        <v>9.041515923</v>
+        <v>9.029893636500001</v>
       </c>
       <c r="P100">
-        <v>45.755550277</v>
+        <v>45.6967344635</v>
       </c>
       <c r="Q100">
-        <v>47.755550277</v>
+        <v>47.6967344635</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.121736863947602</v>
+        <v>4.189501723062772</v>
       </c>
       <c r="T100">
-        <v>40.4638734175917</v>
+        <v>80.76845925045471</v>
       </c>
       <c r="U100">
         <v>0.0535</v>
@@ -9772,91 +9772,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>8.938228554357572</v>
+        <v>8.847943417444867</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.08612079223062775</v>
-      </c>
-      <c r="C101">
-        <v>-15.60628223990173</v>
-      </c>
-      <c r="D101">
-        <v>-91.96288223990172</v>
-      </c>
-      <c r="E101">
-        <v>125.0834</v>
-      </c>
-      <c r="F101">
-        <v>130.3434</v>
-      </c>
-      <c r="G101">
-        <v>206.7</v>
-      </c>
-      <c r="H101">
-        <v>126.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>63.7</v>
-      </c>
-      <c r="K101">
-        <v>2</v>
-      </c>
-      <c r="L101">
-        <v>61.7</v>
-      </c>
-      <c r="M101">
-        <v>6.9733719</v>
-      </c>
-      <c r="N101">
-        <v>54.7266281</v>
-      </c>
-      <c r="O101">
-        <v>9.029893636500001</v>
-      </c>
-      <c r="P101">
-        <v>45.6967344635</v>
-      </c>
-      <c r="Q101">
-        <v>47.6967344635</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.189501723062772</v>
-      </c>
-      <c r="T101">
-        <v>80.76845925045471</v>
-      </c>
-      <c r="U101">
-        <v>0.0535</v>
-      </c>
-      <c r="V101">
-        <v>0.165</v>
-      </c>
-      <c r="W101">
-        <v>0.0446725</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A1/A+</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>8.847943417444867</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
